--- a/data/leagues/Ross' Fantasy League 2026.xlsx
+++ b/data/leagues/Ross' Fantasy League 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="94">
   <si>
     <t>Ross' Sauces</t>
   </si>
@@ -49,13 +49,16 @@
     <t>Yung Killas</t>
   </si>
   <si>
-    <t>0-2-0</t>
-  </si>
-  <si>
-    <t>1-1-0</t>
-  </si>
-  <si>
-    <t>2-0-0</t>
+    <t>0-3-0</t>
+  </si>
+  <si>
+    <t>2-1-0</t>
+  </si>
+  <si>
+    <t>1-2-0</t>
+  </si>
+  <si>
+    <t>3-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -112,6 +115,9 @@
     <t>Week_3</t>
   </si>
   <si>
+    <t>Week_4</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -133,30 +139,30 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Basak Gafoor</t>
+  </si>
+  <si>
+    <t>William Le</t>
+  </si>
+  <si>
+    <t>Tyler Rahman</t>
+  </si>
+  <si>
+    <t>Andrew Ross</t>
+  </si>
+  <si>
+    <t>Michael Nader</t>
+  </si>
+  <si>
+    <t>Alan Devera</t>
+  </si>
+  <si>
     <t>Jackson Jansorn</t>
   </si>
   <si>
-    <t>William Le</t>
-  </si>
-  <si>
-    <t>Basak Gafoor</t>
-  </si>
-  <si>
-    <t>Michael Nader</t>
-  </si>
-  <si>
-    <t>Tyler Rahman</t>
-  </si>
-  <si>
-    <t>Alan Devera</t>
-  </si>
-  <si>
     <t>Nach Konuganti</t>
   </si>
   <si>
-    <t>Andrew Ross</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -181,40 +187,43 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>8.8-4.1-0.2</t>
-  </si>
-  <si>
-    <t>9.6-3.2-0.2</t>
-  </si>
-  <si>
-    <t>7.6-5.2-0.2</t>
-  </si>
-  <si>
-    <t>6.8-6.0-0.2</t>
-  </si>
-  <si>
-    <t>6.7-6.2-0.1</t>
-  </si>
-  <si>
-    <t>5.0-7.8-0.2</t>
-  </si>
-  <si>
-    <t>3.9-8.9-0.2</t>
-  </si>
-  <si>
-    <t>2.9-9.9-0.2</t>
-  </si>
-  <si>
-    <t>9-4</t>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>11.1-1.9-0.1</t>
+  </si>
+  <si>
+    <t>9.5-3.4-0.1</t>
+  </si>
+  <si>
+    <t>8.0-4.9-0.1</t>
+  </si>
+  <si>
+    <t>7.7-5.2-0.1</t>
+  </si>
+  <si>
+    <t>5.7-7.2-0.1</t>
+  </si>
+  <si>
+    <t>3.5-9.4-0.1</t>
+  </si>
+  <si>
+    <t>3.4-9.5-0.1</t>
+  </si>
+  <si>
+    <t>2.8-10.1-0.1</t>
+  </si>
+  <si>
+    <t>11-2</t>
   </si>
   <si>
     <t>10-3</t>
@@ -226,7 +235,7 @@
     <t>7-6</t>
   </si>
   <si>
-    <t>5-8</t>
+    <t>6-7</t>
   </si>
   <si>
     <t>4-9</t>
@@ -235,6 +244,9 @@
     <t>3-10</t>
   </si>
   <si>
+    <t>2-11</t>
+  </si>
+  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -244,31 +256,34 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↓3</t>
-  </si>
-  <si>
-    <t>↑4</t>
+    <t>↑8</t>
+  </si>
+  <si>
+    <t>↑10</t>
+  </si>
+  <si>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↓4</t>
+  </si>
+  <si>
+    <t>↑1</t>
   </si>
   <si>
     <t>↓2</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>↑7</t>
-  </si>
-  <si>
-    <t>↓6</t>
-  </si>
-  <si>
-    <t>↑2</t>
+    <t>↓8</t>
   </si>
   <si>
     <t>Week 1</t>
   </si>
   <si>
     <t>Week 2</t>
+  </si>
+  <si>
+    <t>Week 3</t>
   </si>
   <si>
     <t>Week</t>
@@ -684,25 +699,25 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
         <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -713,7 +728,7 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
@@ -731,7 +746,7 @@
         <v>9</v>
       </c>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -742,16 +757,16 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
         <v>9</v>
@@ -768,25 +783,25 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I5" t="s">
         <v>9</v>
@@ -800,25 +815,25 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6" t="s">
         <v>8</v>
       </c>
       <c r="H6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -826,10 +841,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
         <v>8</v>
@@ -841,10 +856,10 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I7" t="s">
         <v>9</v>
@@ -858,25 +873,25 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>8</v>
       </c>
       <c r="G8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
       </c>
       <c r="I8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -887,10 +902,10 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -899,7 +914,7 @@
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H9" t="s">
         <v>9</v>
@@ -915,30 +930,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -972,24 +987,50 @@
         <v>1</v>
       </c>
       <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
         <v>7</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>6</v>
       </c>
-      <c r="F3">
+      <c r="F4">
         <v>-3</v>
       </c>
-      <c r="G3">
-        <v>9</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="G4">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1005,13 +1046,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1019,10 +1060,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -1033,13 +1074,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1050,10 +1091,10 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1064,7 +1105,7 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>1.375</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
@@ -1075,13 +1116,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>1.125</v>
+        <v>1.75</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1089,13 +1130,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>1.125</v>
+        <v>1.875</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1106,10 +1147,10 @@
         <v>4</v>
       </c>
       <c r="C8">
-        <v>1.25</v>
+        <v>1.875</v>
       </c>
       <c r="D8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1117,13 +1158,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1138,16 +1179,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1155,16 +1196,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="D2">
-        <v>-0.5</v>
+        <v>-0.75</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1172,16 +1213,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="D3">
-        <v>-0.5</v>
+        <v>0.25</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1189,16 +1230,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>-0.75</v>
+        <v>-1</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1206,16 +1247,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>1.625</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>-0.375</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1223,16 +1264,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>0.875</v>
+        <v>1.25</v>
       </c>
       <c r="D6">
-        <v>-0.125</v>
+        <v>0.25</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1240,16 +1281,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0.75</v>
+        <v>1.125</v>
       </c>
       <c r="D7">
-        <v>-0.25</v>
+        <v>1.125</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1257,16 +1298,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="D8">
-        <v>0.625</v>
+        <v>-0.25</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1277,10 +1318,10 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="D9">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1298,57 +1339,57 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>28.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="C2">
-        <v>34.5</v>
+        <v>19.8</v>
       </c>
       <c r="D2">
-        <v>18.3</v>
+        <v>3.2</v>
       </c>
       <c r="E2">
-        <v>12.2</v>
+        <v>0.5</v>
       </c>
       <c r="F2">
-        <v>5.3</v>
+        <v>0.1</v>
       </c>
       <c r="G2">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1362,34 +1403,34 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>56.9</v>
+        <v>19.2</v>
       </c>
       <c r="C3">
-        <v>25.9</v>
+        <v>52.9</v>
       </c>
       <c r="D3">
-        <v>9.5</v>
+        <v>20.6</v>
       </c>
       <c r="E3">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="F3">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="G3">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>99.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1397,164 +1438,164 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>7.3</v>
+        <v>2.4</v>
       </c>
       <c r="C4">
-        <v>15.9</v>
+        <v>13.8</v>
       </c>
       <c r="D4">
-        <v>26.7</v>
+        <v>35.5</v>
       </c>
       <c r="E4">
-        <v>23.6</v>
+        <v>36</v>
       </c>
       <c r="F4">
-        <v>19.4</v>
+        <v>11.4</v>
       </c>
       <c r="G4">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="H4">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B5">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>14.4</v>
+        <v>11.9</v>
       </c>
       <c r="D5">
-        <v>21.6</v>
+        <v>35.3</v>
       </c>
       <c r="E5">
-        <v>22.6</v>
+        <v>37.8</v>
       </c>
       <c r="F5">
-        <v>21.6</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>10.9</v>
+        <v>1.4</v>
       </c>
       <c r="H5">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="I5">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>95.2</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>8.5</v>
+        <v>1.6</v>
       </c>
       <c r="D6">
-        <v>18.8</v>
+        <v>4.9</v>
       </c>
       <c r="E6">
-        <v>23.8</v>
+        <v>16.9</v>
       </c>
       <c r="F6">
-        <v>24.7</v>
+        <v>53.9</v>
       </c>
       <c r="G6">
-        <v>14.5</v>
+        <v>15.1</v>
       </c>
       <c r="H6">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="I6">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J6">
-        <v>93.5</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B7">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>4.1</v>
+        <v>0.3</v>
       </c>
       <c r="E7">
-        <v>8.6</v>
+        <v>1.1</v>
       </c>
       <c r="F7">
-        <v>16.5</v>
+        <v>9.4</v>
       </c>
       <c r="G7">
-        <v>36.7</v>
+        <v>40.2</v>
       </c>
       <c r="H7">
-        <v>24.4</v>
+        <v>25.1</v>
       </c>
       <c r="I7">
-        <v>8.800000000000001</v>
+        <v>23.9</v>
       </c>
       <c r="J7">
-        <v>66.8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B8">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="E8">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="F8">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G8">
-        <v>21.4</v>
+        <v>23.1</v>
       </c>
       <c r="H8">
-        <v>42.3</v>
+        <v>36.8</v>
       </c>
       <c r="I8">
-        <v>23.4</v>
+        <v>30.3</v>
       </c>
       <c r="J8">
-        <v>34.3</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1563,25 +1604,25 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F9">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="G9">
-        <v>9.300000000000001</v>
+        <v>19.1</v>
       </c>
       <c r="H9">
-        <v>22.3</v>
+        <v>31.3</v>
       </c>
       <c r="I9">
-        <v>65.7</v>
+        <v>44.4</v>
       </c>
       <c r="J9">
-        <v>12</v>
+        <v>24.3</v>
       </c>
     </row>
   </sheetData>
@@ -1591,35 +1632,41 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>29</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>44.2</v>
+        <v>43.5</v>
       </c>
       <c r="C2">
         <v>100</v>
       </c>
       <c r="D2">
-        <v>99.90000000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>100</v>
+      </c>
+      <c r="E2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1627,94 +1674,115 @@
         <v>100</v>
       </c>
       <c r="C3">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="D3">
         <v>100</v>
       </c>
-      <c r="D3">
-        <v>99.90000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>97.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="C4">
+        <v>98.5</v>
+      </c>
+      <c r="D4">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="E4">
+        <v>99.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>0.1</v>
+      </c>
+      <c r="C5">
+        <v>92.2</v>
+      </c>
+      <c r="D5">
         <v>99.2</v>
       </c>
-      <c r="D4">
-        <v>98.8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="C5">
-        <v>96.2</v>
-      </c>
-      <c r="D5">
-        <v>95.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5">
+        <v>99.59999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>0.1</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="C6">
-        <v>94.3</v>
+        <v>13.2</v>
       </c>
       <c r="D6">
         <v>93.7</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6">
+        <v>92.40000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7">
+        <v>88</v>
+      </c>
+      <c r="C7">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="D7">
+        <v>50.6</v>
+      </c>
+      <c r="E7">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B7">
-        <v>96.5</v>
-      </c>
-      <c r="C7">
-        <v>64.8</v>
-      </c>
-      <c r="D7">
-        <v>65.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="B8">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="C8">
+        <v>65.5</v>
+      </c>
+      <c r="D8">
+        <v>30.2</v>
+      </c>
+      <c r="E8">
+        <v>32.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="C8">
-        <v>33.7</v>
-      </c>
-      <c r="D8">
-        <v>34.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="B9">
-        <v>88.7</v>
+        <v>83.5</v>
       </c>
       <c r="C9">
-        <v>11.8</v>
+        <v>35.09999999999999</v>
       </c>
       <c r="D9">
-        <v>12</v>
+        <v>26.4</v>
+      </c>
+      <c r="E9">
+        <v>26.9</v>
       </c>
     </row>
   </sheetData>
@@ -1729,28 +1797,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1758,28 +1826,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2">
-        <v>152.83</v>
+        <v>117.04</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2">
-        <v>138.84</v>
+        <v>145.16</v>
       </c>
       <c r="G2">
-        <v>0.409</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H2">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1790,25 +1858,25 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3">
-        <v>132.34</v>
+        <v>120.51</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3">
-        <v>141.18</v>
+        <v>142.82</v>
       </c>
       <c r="G3">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="H3">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1816,28 +1884,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4">
-        <v>132.19</v>
+        <v>142.21</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>140.6</v>
+        <v>142.24</v>
       </c>
       <c r="G4">
-        <v>0.545</v>
+        <v>0.467</v>
       </c>
       <c r="H4">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1845,28 +1913,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5">
-        <v>141.28</v>
+        <v>127.1</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>139.29</v>
+        <v>144.44</v>
       </c>
       <c r="G5">
-        <v>0.545</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1874,28 +1942,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D6">
-        <v>140.2</v>
+        <v>147</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>138.81</v>
+        <v>139.56</v>
       </c>
       <c r="G6">
-        <v>0.455</v>
+        <v>0.533</v>
       </c>
       <c r="H6">
-        <v>-0.4</v>
+        <v>0.1</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1906,25 +1974,25 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D7">
-        <v>149.17</v>
+        <v>163.71</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>141.05</v>
+        <v>137.22</v>
       </c>
       <c r="G7">
         <v>0.5</v>
       </c>
       <c r="H7">
-        <v>-0.5</v>
+        <v>-1.5</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1932,28 +2000,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D8">
-        <v>124.87</v>
+        <v>167.72</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F8">
-        <v>140.57</v>
+        <v>131.65</v>
       </c>
       <c r="G8">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="H8">
-        <v>-0.6</v>
+        <v>-2.5</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1961,28 +2029,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9">
-        <v>146.74</v>
+        <v>134.31</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>139.28</v>
+        <v>136.51</v>
       </c>
       <c r="G9">
-        <v>0.545</v>
+        <v>0.5</v>
       </c>
       <c r="H9">
-        <v>-0.8</v>
+        <v>-2.6</v>
       </c>
       <c r="I9">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1997,48 +2065,48 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>149.17</v>
+        <v>167.72</v>
       </c>
       <c r="E2">
-        <v>298.34</v>
+        <v>503.16</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2047,39 +2115,39 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D3">
-        <v>152.83</v>
+        <v>163.7066666666667</v>
       </c>
       <c r="E3">
-        <v>305.66</v>
+        <v>491.12</v>
       </c>
       <c r="F3">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="G3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2087,173 +2155,173 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>140.2</v>
+        <v>142.2133333333333</v>
       </c>
       <c r="E4">
-        <v>280.4</v>
+        <v>426.64</v>
       </c>
       <c r="F4">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D5">
-        <v>146.74</v>
+        <v>147</v>
       </c>
       <c r="E5">
-        <v>293.48</v>
+        <v>441</v>
       </c>
       <c r="F5">
-        <v>95.19999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="G5">
-        <v>0.8999999999999999</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D6">
-        <v>141.28</v>
+        <v>134.3133333333333</v>
       </c>
       <c r="E6">
-        <v>282.56</v>
+        <v>402.94</v>
       </c>
       <c r="F6">
-        <v>93.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="G6">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="H6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>132.19</v>
+        <v>127.1</v>
       </c>
       <c r="E7">
-        <v>264.38</v>
+        <v>381.3</v>
       </c>
       <c r="F7">
-        <v>66.8</v>
+        <v>51</v>
       </c>
       <c r="G7">
-        <v>8.799999999999999</v>
+        <v>23.9</v>
       </c>
       <c r="H7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D8">
-        <v>132.34</v>
+        <v>117.04</v>
       </c>
       <c r="E8">
-        <v>264.68</v>
+        <v>351.12</v>
       </c>
       <c r="F8">
-        <v>34.3</v>
+        <v>32.9</v>
       </c>
       <c r="G8">
-        <v>23.4</v>
+        <v>30.3</v>
       </c>
       <c r="H8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>124.87</v>
+        <v>120.5133333333333</v>
       </c>
       <c r="E9">
-        <v>249.74</v>
+        <v>361.54</v>
       </c>
       <c r="F9">
-        <v>12</v>
+        <v>24.3</v>
       </c>
       <c r="G9">
-        <v>65.7</v>
+        <v>44.4</v>
       </c>
       <c r="H9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -2268,19 +2336,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2291,16 +2359,16 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2308,19 +2376,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2331,16 +2399,16 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2348,19 +2416,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2368,19 +2436,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2388,19 +2456,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D7">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2411,16 +2479,16 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D8">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2428,19 +2496,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D9">
-        <v>-6</v>
+        <v>-14</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -2450,21 +2518,24 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>86</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -2474,25 +2545,31 @@
       <c r="C2">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="D2">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="C3">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>-6</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -2502,53 +2579,65 @@
       <c r="C4">
         <v>4</v>
       </c>
-      <c r="D4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>4</v>
       </c>
-      <c r="C5">
+      <c r="C6">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6">
+      <c r="B7">
         <v>-10</v>
       </c>
-      <c r="C6">
+      <c r="C7">
         <v>-3</v>
       </c>
-      <c r="D6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>-6</v>
-      </c>
-      <c r="D7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="D7">
+        <v>-2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -2558,22 +2647,28 @@
       <c r="C8">
         <v>-6</v>
       </c>
-      <c r="D8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="D8">
+        <v>-8</v>
+      </c>
+      <c r="E8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B9">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="C9">
         <v>-6</v>
       </c>
-      <c r="D9" t="s">
-        <v>79</v>
+      <c r="D9">
+        <v>-14</v>
+      </c>
+      <c r="E9" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Ross' Fantasy League 2026.xlsx
+++ b/data/leagues/Ross' Fantasy League 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="94">
   <si>
     <t>Ross' Sauces</t>
   </si>
@@ -49,16 +49,19 @@
     <t>Yung Killas</t>
   </si>
   <si>
-    <t>0-3-0</t>
-  </si>
-  <si>
-    <t>2-1-0</t>
-  </si>
-  <si>
-    <t>1-2-0</t>
-  </si>
-  <si>
-    <t>3-0-0</t>
+    <t>0-4-0</t>
+  </si>
+  <si>
+    <t>3-1-0</t>
+  </si>
+  <si>
+    <t>2-2-0</t>
+  </si>
+  <si>
+    <t>1-3-0</t>
+  </si>
+  <si>
+    <t>4-0-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -118,6 +121,9 @@
     <t>Week_4</t>
   </si>
   <si>
+    <t>Week_5</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -139,30 +145,30 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Michael Nader</t>
+  </si>
+  <si>
     <t>Basak Gafoor</t>
   </si>
   <si>
+    <t>Andrew Ross</t>
+  </si>
+  <si>
     <t>William Le</t>
   </si>
   <si>
     <t>Tyler Rahman</t>
   </si>
   <si>
-    <t>Andrew Ross</t>
-  </si>
-  <si>
-    <t>Michael Nader</t>
+    <t>Nach Konuganti</t>
+  </si>
+  <si>
+    <t>Jackson Jansorn</t>
   </si>
   <si>
     <t>Alan Devera</t>
   </si>
   <si>
-    <t>Jackson Jansorn</t>
-  </si>
-  <si>
-    <t>Nach Konuganti</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -187,40 +193,37 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>0-3</t>
-  </si>
-  <si>
-    <t>11.1-1.9-0.1</t>
-  </si>
-  <si>
-    <t>9.5-3.4-0.1</t>
-  </si>
-  <si>
-    <t>8.0-4.9-0.1</t>
-  </si>
-  <si>
-    <t>7.7-5.2-0.1</t>
-  </si>
-  <si>
-    <t>5.7-7.2-0.1</t>
-  </si>
-  <si>
-    <t>3.5-9.4-0.1</t>
-  </si>
-  <si>
-    <t>3.4-9.5-0.1</t>
-  </si>
-  <si>
-    <t>2.8-10.1-0.1</t>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>0-4</t>
+  </si>
+  <si>
+    <t>10.9-2.0-0.1</t>
+  </si>
+  <si>
+    <t>9.4-3.5-0.1</t>
+  </si>
+  <si>
+    <t>8.3-4.6-0.1</t>
+  </si>
+  <si>
+    <t>6.0-6.9-0.1</t>
+  </si>
+  <si>
+    <t>4.8-8.1-0.1</t>
+  </si>
+  <si>
+    <t>4.5-8.5-0.1</t>
+  </si>
+  <si>
+    <t>3.0-9.9-0.1</t>
   </si>
   <si>
     <t>11-2</t>
@@ -229,24 +232,21 @@
     <t>10-3</t>
   </si>
   <si>
-    <t>8-5</t>
-  </si>
-  <si>
-    <t>7-6</t>
+    <t>9-4</t>
   </si>
   <si>
     <t>6-7</t>
   </si>
   <si>
+    <t>5-8</t>
+  </si>
+  <si>
     <t>4-9</t>
   </si>
   <si>
     <t>3-10</t>
   </si>
   <si>
-    <t>2-11</t>
-  </si>
-  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -256,27 +256,24 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑8</t>
-  </si>
-  <si>
-    <t>↑10</t>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↑4</t>
   </si>
   <si>
     <t>↓1</t>
   </si>
   <si>
+    <t>↓5</t>
+  </si>
+  <si>
+    <t>↑5</t>
+  </si>
+  <si>
     <t>↓4</t>
   </si>
   <si>
-    <t>↑1</t>
-  </si>
-  <si>
-    <t>↓2</t>
-  </si>
-  <si>
-    <t>↓8</t>
-  </si>
-  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -284,6 +281,9 @@
   </si>
   <si>
     <t>Week 3</t>
+  </si>
+  <si>
+    <t>Week 4</t>
   </si>
   <si>
     <t>Week</t>
@@ -699,13 +699,13 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
@@ -714,10 +714,10 @@
         <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -728,10 +728,10 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -740,13 +740,13 @@
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H3" t="s">
         <v>9</v>
       </c>
       <c r="I3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -754,28 +754,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
       </c>
       <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H4" t="s">
         <v>9</v>
       </c>
       <c r="I4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -792,13 +792,13 @@
         <v>9</v>
       </c>
       <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
         <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" t="s">
-        <v>10</v>
       </c>
       <c r="H5" t="s">
         <v>9</v>
@@ -812,7 +812,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
@@ -841,7 +841,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -850,19 +850,19 @@
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -870,7 +870,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
@@ -882,13 +882,13 @@
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G8" t="s">
         <v>10</v>
       </c>
       <c r="H8" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I8" t="s">
         <v>10</v>
@@ -899,28 +899,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -930,7 +930,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -961,25 +961,25 @@
         <v>0</v>
       </c>
       <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
-        <v>1</v>
-      </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>-6</v>
+        <v>15</v>
       </c>
       <c r="F2">
         <v>4</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -987,19 +987,19 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G3">
         <v>10</v>
@@ -1013,25 +1013,103 @@
         <v>2</v>
       </c>
       <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
         <v>2</v>
       </c>
-      <c r="C4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>14</v>
+      </c>
+      <c r="G4">
+        <v>10</v>
+      </c>
+      <c r="H4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
         <v>7</v>
       </c>
-      <c r="E4">
+      <c r="E5">
         <v>6</v>
       </c>
-      <c r="F4">
+      <c r="F5">
         <v>-3</v>
       </c>
-      <c r="G4">
+      <c r="G5">
         <v>9</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H5" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>-6</v>
+      </c>
+      <c r="F6">
+        <v>-15</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>-3</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>7</v>
+      </c>
+      <c r="H7" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1046,13 +1124,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1060,13 +1138,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1074,10 +1152,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>1.375</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1088,13 +1166,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>1.125</v>
+        <v>1.5</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1105,10 +1183,10 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>1.375</v>
+        <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1119,10 +1197,10 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>1.75</v>
+        <v>2.125</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1130,13 +1208,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>1.875</v>
+        <v>2.5</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1144,13 +1222,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>1.875</v>
+        <v>2.625</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1158,13 +1236,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1179,16 +1257,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1199,13 +1277,13 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>2.25</v>
+        <v>2.875</v>
       </c>
       <c r="D2">
-        <v>-0.75</v>
+        <v>-1.125</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1213,16 +1291,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>2.25</v>
+        <v>2.875</v>
       </c>
       <c r="D3">
-        <v>0.25</v>
+        <v>-1.125</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1230,16 +1308,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>2.625</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>0.625</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1247,16 +1325,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>1.625</v>
+        <v>1.75</v>
       </c>
       <c r="D5">
-        <v>-0.375</v>
+        <v>0.75</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1264,13 +1342,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>1.25</v>
+        <v>1.625</v>
       </c>
       <c r="D6">
-        <v>0.25</v>
+        <v>-0.375</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -1281,16 +1359,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>1.125</v>
+        <v>1.5</v>
       </c>
       <c r="D7">
-        <v>1.125</v>
+        <v>-0.5</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1298,16 +1376,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="D8">
-        <v>-0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1315,13 +1393,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="D9">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1339,34 +1417,34 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -1374,19 +1452,19 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>76.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="C2">
-        <v>19.8</v>
+        <v>17.2</v>
       </c>
       <c r="D2">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="E2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1403,25 +1481,25 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3">
-        <v>19.2</v>
+        <v>14.7</v>
       </c>
       <c r="C3">
-        <v>52.9</v>
+        <v>47.6</v>
       </c>
       <c r="D3">
-        <v>20.6</v>
+        <v>31.2</v>
       </c>
       <c r="E3">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="F3">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="G3">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1435,34 +1513,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4">
+        <v>6.5</v>
+      </c>
+      <c r="C4">
+        <v>32.2</v>
+      </c>
+      <c r="D4">
+        <v>49.3</v>
+      </c>
+      <c r="E4">
+        <v>9.1</v>
+      </c>
+      <c r="F4">
         <v>2.4</v>
       </c>
-      <c r="C4">
-        <v>13.8</v>
-      </c>
-      <c r="D4">
-        <v>35.5</v>
-      </c>
-      <c r="E4">
-        <v>36</v>
-      </c>
-      <c r="F4">
-        <v>11.4</v>
-      </c>
       <c r="G4">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1470,31 +1548,31 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="C5">
-        <v>11.9</v>
+        <v>2.8</v>
       </c>
       <c r="D5">
-        <v>35.3</v>
+        <v>11.4</v>
       </c>
       <c r="E5">
-        <v>37.8</v>
+        <v>44.7</v>
       </c>
       <c r="F5">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>1.4</v>
+        <v>12.2</v>
       </c>
       <c r="H5">
-        <v>0.6</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J5">
-        <v>99.40000000000001</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1505,65 +1583,65 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>1.6</v>
+        <v>0.2</v>
       </c>
       <c r="D6">
-        <v>4.9</v>
+        <v>1.8</v>
       </c>
       <c r="E6">
-        <v>16.9</v>
+        <v>16.1</v>
       </c>
       <c r="F6">
-        <v>53.9</v>
+        <v>28.5</v>
       </c>
       <c r="G6">
-        <v>15.1</v>
+        <v>22.1</v>
       </c>
       <c r="H6">
-        <v>6.2</v>
+        <v>22.1</v>
       </c>
       <c r="I6">
-        <v>1.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J6">
-        <v>92.40000000000001</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="E7">
-        <v>1.1</v>
+        <v>10.2</v>
       </c>
       <c r="F7">
-        <v>9.4</v>
+        <v>21.7</v>
       </c>
       <c r="G7">
-        <v>40.2</v>
+        <v>28.7</v>
       </c>
       <c r="H7">
-        <v>25.1</v>
+        <v>25.9</v>
       </c>
       <c r="I7">
-        <v>23.9</v>
+        <v>12.3</v>
       </c>
       <c r="J7">
-        <v>51</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1572,30 +1650,30 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="E8">
-        <v>1.3</v>
+        <v>11.5</v>
       </c>
       <c r="F8">
-        <v>8.300000000000001</v>
+        <v>22.1</v>
       </c>
       <c r="G8">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="H8">
-        <v>36.8</v>
+        <v>26</v>
       </c>
       <c r="I8">
-        <v>30.3</v>
+        <v>16</v>
       </c>
       <c r="J8">
-        <v>32.9</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1604,25 +1682,25 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E9">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="F9">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="G9">
-        <v>19.1</v>
+        <v>13.3</v>
       </c>
       <c r="H9">
-        <v>31.3</v>
+        <v>18.9</v>
       </c>
       <c r="I9">
-        <v>44.4</v>
+        <v>60</v>
       </c>
       <c r="J9">
-        <v>24.3</v>
+        <v>21.1</v>
       </c>
     </row>
   </sheetData>
@@ -1632,29 +1710,32 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>31</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>43.5</v>
+        <v>39.90000000000001</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -1665,124 +1746,148 @@
       <c r="E2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="C3">
-        <v>99.90000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="D3">
         <v>100</v>
       </c>
       <c r="E3">
+        <v>99.8</v>
+      </c>
+      <c r="F3">
+        <v>99.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>98.90000000000001</v>
-      </c>
       <c r="C4">
-        <v>98.5</v>
+        <v>100</v>
       </c>
       <c r="D4">
+        <v>100</v>
+      </c>
+      <c r="E4">
         <v>99.90000000000001</v>
       </c>
-      <c r="E4">
-        <v>99.8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4">
+        <v>99.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>92.2</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="D5">
-        <v>99.2</v>
+        <v>99.8</v>
       </c>
       <c r="E5">
-        <v>99.59999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>93.89999999999999</v>
+      </c>
+      <c r="F5">
+        <v>93.10000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>89.90000000000001</v>
+        <v>90.10000000000001</v>
       </c>
       <c r="C6">
-        <v>13.2</v>
+        <v>12.4</v>
       </c>
       <c r="D6">
-        <v>93.7</v>
+        <v>92.60000000000001</v>
       </c>
       <c r="E6">
-        <v>92.40000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="F6">
+        <v>67.90000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B7">
-        <v>88</v>
+        <v>96.89999999999999</v>
       </c>
       <c r="C7">
-        <v>95.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="D7">
-        <v>50.6</v>
+        <v>34.5</v>
       </c>
       <c r="E7">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>56.89999999999999</v>
+      </c>
+      <c r="F7">
+        <v>60.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B8">
-        <v>96.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="C8">
-        <v>65.5</v>
+        <v>34.9</v>
       </c>
       <c r="D8">
-        <v>30.2</v>
+        <v>24.2</v>
       </c>
       <c r="E8">
-        <v>32.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>59</v>
+      </c>
+      <c r="F8">
+        <v>59.59999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B9">
-        <v>83.5</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="C9">
-        <v>35.09999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="D9">
-        <v>26.4</v>
+        <v>48.9</v>
       </c>
       <c r="E9">
-        <v>26.9</v>
+        <v>16.6</v>
+      </c>
+      <c r="F9">
+        <v>19.7</v>
       </c>
     </row>
   </sheetData>
@@ -1797,28 +1902,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1826,28 +1931,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D2">
-        <v>117.04</v>
+        <v>139.09</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2">
-        <v>145.16</v>
+        <v>142.52</v>
       </c>
       <c r="G2">
-        <v>0.5669999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="H2">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1855,28 +1960,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3">
-        <v>120.51</v>
+        <v>125.65</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>142.82</v>
+        <v>143.26</v>
       </c>
       <c r="G3">
-        <v>0.533</v>
+        <v>0.528</v>
       </c>
       <c r="H3">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1884,28 +1989,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D4">
-        <v>142.21</v>
+        <v>126.32</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>142.24</v>
+        <v>142.26</v>
       </c>
       <c r="G4">
-        <v>0.467</v>
+        <v>0.528</v>
       </c>
       <c r="H4">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1913,28 +2018,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D5">
-        <v>127.1</v>
+        <v>131.27</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>144.44</v>
+        <v>141.88</v>
       </c>
       <c r="G5">
-        <v>0.5669999999999999</v>
+        <v>0.528</v>
       </c>
       <c r="H5">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1942,28 +2047,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D6">
-        <v>147</v>
+        <v>146.32</v>
       </c>
       <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>138.4</v>
+      </c>
+      <c r="G6">
+        <v>0.417</v>
+      </c>
+      <c r="H6">
+        <v>-0.8</v>
+      </c>
+      <c r="I6">
         <v>9</v>
-      </c>
-      <c r="F6">
-        <v>139.56</v>
-      </c>
-      <c r="G6">
-        <v>0.533</v>
-      </c>
-      <c r="H6">
-        <v>0.1</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1971,28 +2076,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D7">
-        <v>163.71</v>
+        <v>133.12</v>
       </c>
       <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7">
+        <v>139.84</v>
+      </c>
+      <c r="G7">
+        <v>0.583</v>
+      </c>
+      <c r="H7">
+        <v>-1.8</v>
+      </c>
+      <c r="I7">
         <v>9</v>
-      </c>
-      <c r="F7">
-        <v>137.22</v>
-      </c>
-      <c r="G7">
-        <v>0.5</v>
-      </c>
-      <c r="H7">
-        <v>-1.5</v>
-      </c>
-      <c r="I7">
-        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2003,25 +2108,25 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D8">
-        <v>167.72</v>
+        <v>162.16</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>131.65</v>
+        <v>134.94</v>
       </c>
       <c r="G8">
-        <v>0.333</v>
+        <v>0.417</v>
       </c>
       <c r="H8">
-        <v>-2.5</v>
+        <v>-2.4</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2029,28 +2134,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D9">
-        <v>134.31</v>
+        <v>155.74</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9">
-        <v>136.51</v>
+        <v>136.59</v>
       </c>
       <c r="G9">
-        <v>0.5</v>
+        <v>0.444</v>
       </c>
       <c r="H9">
-        <v>-2.6</v>
+        <v>-2.8</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2065,31 +2170,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2097,16 +2202,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>167.72</v>
+        <v>162.165</v>
       </c>
       <c r="E2">
-        <v>503.16</v>
+        <v>648.66</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2115,27 +2220,27 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C3">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>163.7066666666667</v>
+        <v>146.325</v>
       </c>
       <c r="E3">
-        <v>491.12</v>
+        <v>585.3</v>
       </c>
       <c r="F3">
         <v>100</v>
@@ -2144,39 +2249,39 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D4">
-        <v>142.2133333333333</v>
+        <v>155.735</v>
       </c>
       <c r="E4">
-        <v>426.64</v>
+        <v>622.9400000000001</v>
       </c>
       <c r="F4">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2184,28 +2289,28 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C5">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D5">
-        <v>147</v>
+        <v>139.095</v>
       </c>
       <c r="E5">
-        <v>441</v>
+        <v>556.38</v>
       </c>
       <c r="F5">
-        <v>99.40000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="H5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2213,54 +2318,54 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C6">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="D6">
-        <v>134.3133333333333</v>
+        <v>133.12</v>
       </c>
       <c r="E6">
-        <v>402.94</v>
+        <v>532.48</v>
       </c>
       <c r="F6">
-        <v>92.40000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="G6">
-        <v>1.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
         <v>57</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>127.1</v>
+        <v>125.645</v>
       </c>
       <c r="E7">
-        <v>381.3</v>
+        <v>502.58</v>
       </c>
       <c r="F7">
-        <v>51</v>
+        <v>61.8</v>
       </c>
       <c r="G7">
-        <v>23.9</v>
+        <v>12.3</v>
       </c>
       <c r="H7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I7" t="s">
         <v>71</v>
@@ -2268,28 +2373,28 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C8">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="D8">
-        <v>117.04</v>
+        <v>131.265</v>
       </c>
       <c r="E8">
-        <v>351.12</v>
+        <v>525.0600000000001</v>
       </c>
       <c r="F8">
-        <v>32.9</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="G8">
-        <v>30.3</v>
+        <v>16</v>
       </c>
       <c r="H8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I8" t="s">
         <v>72</v>
@@ -2297,28 +2402,28 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>120.5133333333333</v>
+        <v>126.32</v>
       </c>
       <c r="E9">
-        <v>361.54</v>
+        <v>505.28</v>
       </c>
       <c r="F9">
-        <v>24.3</v>
+        <v>21.1</v>
       </c>
       <c r="G9">
-        <v>44.4</v>
+        <v>60</v>
       </c>
       <c r="H9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I9" t="s">
         <v>73</v>
@@ -2336,7 +2441,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>74</v>
@@ -2345,7 +2450,7 @@
         <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>76</v>
@@ -2359,13 +2464,13 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
         <v>77</v>
@@ -2376,10 +2481,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D3">
         <v>4</v>
@@ -2388,7 +2493,7 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2396,19 +2501,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2416,19 +2521,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2436,16 +2541,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
         <v>80</v>
@@ -2456,16 +2561,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>81</v>
@@ -2476,16 +2581,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D8">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>82</v>
@@ -2499,16 +2604,16 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2518,24 +2623,27 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -2548,113 +2656,134 @@
       <c r="D2">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B5">
         <v>-8</v>
       </c>
-      <c r="C3">
+      <c r="C5">
         <v>-6</v>
       </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
         <v>6</v>
       </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5">
+      <c r="D6">
         <v>2</v>
       </c>
-      <c r="C5">
+      <c r="E6">
+        <v>-3</v>
+      </c>
+      <c r="F6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
+      <c r="B7">
+        <v>-3</v>
+      </c>
+      <c r="C7">
+        <v>-6</v>
+      </c>
+      <c r="D7">
+        <v>-8</v>
+      </c>
+      <c r="E7">
+        <v>-3</v>
+      </c>
+      <c r="F7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>-10</v>
       </c>
-      <c r="C7">
+      <c r="C8">
         <v>-3</v>
       </c>
-      <c r="D7">
+      <c r="D8">
         <v>-2</v>
       </c>
-      <c r="E7" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>-3</v>
-      </c>
-      <c r="C8">
+      <c r="E8">
         <v>-6</v>
       </c>
-      <c r="D8">
-        <v>-8</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -2667,8 +2796,11 @@
       <c r="D9">
         <v>-14</v>
       </c>
-      <c r="E9" t="s">
-        <v>83</v>
+      <c r="E9">
+        <v>-15</v>
+      </c>
+      <c r="F9" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Ross' Fantasy League 2026.xlsx
+++ b/data/leagues/Ross' Fantasy League 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="98">
   <si>
     <t>Ross' Sauces</t>
   </si>
@@ -49,19 +49,22 @@
     <t>Yung Killas</t>
   </si>
   <si>
-    <t>0-4-0</t>
-  </si>
-  <si>
-    <t>3-1-0</t>
-  </si>
-  <si>
-    <t>2-2-0</t>
-  </si>
-  <si>
-    <t>1-3-0</t>
-  </si>
-  <si>
-    <t>4-0-0</t>
+    <t>0-5-0</t>
+  </si>
+  <si>
+    <t>3-2-0</t>
+  </si>
+  <si>
+    <t>2-3-0</t>
+  </si>
+  <si>
+    <t>1-4-0</t>
+  </si>
+  <si>
+    <t>5-0-0</t>
+  </si>
+  <si>
+    <t>4-1-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -124,6 +127,9 @@
     <t>Week_5</t>
   </si>
   <si>
+    <t>Week_6</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -145,30 +151,30 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Basak Gafoor</t>
+  </si>
+  <si>
     <t>Michael Nader</t>
   </si>
   <si>
-    <t>Basak Gafoor</t>
+    <t>Nach Konuganti</t>
+  </si>
+  <si>
+    <t>William Le</t>
   </si>
   <si>
     <t>Andrew Ross</t>
   </si>
   <si>
-    <t>William Le</t>
-  </si>
-  <si>
     <t>Tyler Rahman</t>
   </si>
   <si>
-    <t>Nach Konuganti</t>
+    <t>Alan Devera</t>
   </si>
   <si>
     <t>Jackson Jansorn</t>
   </si>
   <si>
-    <t>Alan Devera</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -193,49 +199,52 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>4-0</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>0-4</t>
-  </si>
-  <si>
-    <t>10.9-2.0-0.1</t>
-  </si>
-  <si>
-    <t>9.4-3.5-0.1</t>
-  </si>
-  <si>
-    <t>8.3-4.6-0.1</t>
-  </si>
-  <si>
-    <t>6.0-6.9-0.1</t>
-  </si>
-  <si>
-    <t>4.8-8.1-0.1</t>
-  </si>
-  <si>
-    <t>4.5-8.5-0.1</t>
-  </si>
-  <si>
-    <t>3.0-9.9-0.1</t>
+    <t>5-0</t>
+  </si>
+  <si>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>0-5</t>
+  </si>
+  <si>
+    <t>10.7-2.2-0.1</t>
+  </si>
+  <si>
+    <t>9.1-3.8-0.1</t>
+  </si>
+  <si>
+    <t>8.7-4.2-0.1</t>
+  </si>
+  <si>
+    <t>6.9-6.0-0.1</t>
+  </si>
+  <si>
+    <t>5.3-7.6-0.1</t>
+  </si>
+  <si>
+    <t>4.3-8.6-0.1</t>
+  </si>
+  <si>
+    <t>3.8-9.1-0.1</t>
+  </si>
+  <si>
+    <t>2.8-10.2-0.1</t>
   </si>
   <si>
     <t>11-2</t>
   </si>
   <si>
-    <t>10-3</t>
-  </si>
-  <si>
     <t>9-4</t>
   </si>
   <si>
-    <t>6-7</t>
+    <t>7-6</t>
   </si>
   <si>
     <t>5-8</t>
@@ -256,22 +265,22 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑5</t>
+  </si>
+  <si>
     <t>↑1</t>
   </si>
   <si>
-    <t>↑4</t>
+    <t>↑8</t>
   </si>
   <si>
     <t>↓1</t>
   </si>
   <si>
-    <t>↓5</t>
-  </si>
-  <si>
-    <t>↑5</t>
-  </si>
-  <si>
-    <t>↓4</t>
+    <t>↓10</t>
+  </si>
+  <si>
+    <t>↓7</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -284,6 +293,9 @@
   </si>
   <si>
     <t>Week 4</t>
+  </si>
+  <si>
+    <t>Week 5</t>
   </si>
   <si>
     <t>Week</t>
@@ -708,10 +720,10 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
@@ -731,19 +743,19 @@
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I3" t="s">
         <v>9</v>
@@ -754,28 +766,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -786,22 +798,22 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I5" t="s">
         <v>9</v>
@@ -824,10 +836,10 @@
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
         <v>10</v>
@@ -876,16 +888,16 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
@@ -902,25 +914,25 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" t="s">
         <v>10</v>
       </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" t="s">
-        <v>11</v>
-      </c>
       <c r="H9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -930,30 +942,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -961,25 +973,25 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>-22</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="G2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -987,25 +999,25 @@
         <v>1</v>
       </c>
       <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>-6</v>
+        <v>15</v>
       </c>
       <c r="F3">
         <v>4</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1013,19 +1025,19 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G4">
         <v>10</v>
@@ -1039,25 +1051,25 @@
         <v>3</v>
       </c>
       <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
         <v>2</v>
       </c>
-      <c r="C5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
       <c r="E5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>-3</v>
+        <v>14</v>
       </c>
       <c r="G5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1065,25 +1077,25 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
         <v>7</v>
       </c>
-      <c r="D6" t="s">
-        <v>4</v>
-      </c>
       <c r="E6">
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>-15</v>
+        <v>-3</v>
       </c>
       <c r="G6">
         <v>9</v>
       </c>
       <c r="H6" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1094,22 +1106,74 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7">
+        <v>-6</v>
+      </c>
+      <c r="F7">
+        <v>-15</v>
+      </c>
+      <c r="G7">
+        <v>9</v>
+      </c>
+      <c r="H7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="D7" t="s">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
         <v>5</v>
       </c>
-      <c r="E7">
+      <c r="E8">
         <v>-3</v>
       </c>
-      <c r="F7">
-        <v>4</v>
-      </c>
-      <c r="G7">
+      <c r="F8">
+        <v>4</v>
+      </c>
+      <c r="G8">
         <v>7</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H8" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9">
+        <v>9</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <v>7</v>
+      </c>
+      <c r="H9" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1124,13 +1188,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1138,13 +1202,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>1.125</v>
+        <v>1.625</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1155,10 +1219,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>1.375</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1166,13 +1230,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1180,13 +1244,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>2.375</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1194,13 +1258,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>2.125</v>
+        <v>2.5</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1211,10 +1275,10 @@
         <v>3</v>
       </c>
       <c r="C7">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1225,7 +1289,7 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>2.625</v>
+        <v>3.125</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
@@ -1239,10 +1303,10 @@
         <v>4</v>
       </c>
       <c r="C9">
-        <v>2.75</v>
+        <v>3.625</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1257,16 +1321,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1274,16 +1338,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>2.875</v>
+        <v>3.625</v>
       </c>
       <c r="D2">
-        <v>-1.125</v>
+        <v>0.625</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1291,13 +1355,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>2.875</v>
+        <v>3.5</v>
       </c>
       <c r="D3">
-        <v>-1.125</v>
+        <v>-1.5</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1308,16 +1372,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>2.625</v>
+        <v>3.5</v>
       </c>
       <c r="D4">
-        <v>0.625</v>
+        <v>-0.5</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1325,16 +1389,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="D5">
-        <v>0.75</v>
+        <v>-0.5</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1342,16 +1406,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>1.625</v>
+        <v>2.125</v>
       </c>
       <c r="D6">
-        <v>-0.375</v>
+        <v>1.125</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1362,13 +1426,13 @@
         <v>4</v>
       </c>
       <c r="C7">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="D7">
-        <v>-0.5</v>
+        <v>-1.25</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1396,10 +1460,10 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="D9">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1417,34 +1481,34 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -1452,13 +1516,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>78.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="C2">
-        <v>17.2</v>
+        <v>23.2</v>
       </c>
       <c r="D2">
-        <v>3.9</v>
+        <v>7.3</v>
       </c>
       <c r="E2">
         <v>0.6</v>
@@ -1484,22 +1548,22 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>14.7</v>
+        <v>13.9</v>
       </c>
       <c r="C3">
-        <v>47.6</v>
+        <v>35.4</v>
       </c>
       <c r="D3">
-        <v>31.2</v>
+        <v>38</v>
       </c>
       <c r="E3">
-        <v>5.7</v>
+        <v>11.7</v>
       </c>
       <c r="F3">
         <v>0.7</v>
       </c>
       <c r="G3">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1516,31 +1580,31 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>6.5</v>
+        <v>15.9</v>
       </c>
       <c r="C4">
-        <v>32.2</v>
+        <v>36.5</v>
       </c>
       <c r="D4">
-        <v>49.3</v>
+        <v>34.8</v>
       </c>
       <c r="E4">
-        <v>9.1</v>
+        <v>10.7</v>
       </c>
       <c r="F4">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="G4">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1548,39 +1612,39 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="C5">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="D5">
-        <v>11.4</v>
+        <v>17.3</v>
       </c>
       <c r="E5">
-        <v>44.7</v>
+        <v>56</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>14.1</v>
       </c>
       <c r="G5">
-        <v>12.2</v>
+        <v>5.4</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>1.4</v>
       </c>
       <c r="I5">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>90.5</v>
+        <v>98.59999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C6">
         <v>0.2</v>
@@ -1589,59 +1653,59 @@
         <v>1.8</v>
       </c>
       <c r="E6">
-        <v>16.1</v>
+        <v>11.1</v>
       </c>
       <c r="F6">
-        <v>28.5</v>
+        <v>37.5</v>
       </c>
       <c r="G6">
-        <v>22.1</v>
+        <v>28.8</v>
       </c>
       <c r="H6">
-        <v>22.1</v>
+        <v>14.9</v>
       </c>
       <c r="I6">
-        <v>9.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="J6">
-        <v>68.7</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <v>0.1</v>
       </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
       <c r="D7">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="E7">
-        <v>10.2</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>21.7</v>
+        <v>24.2</v>
       </c>
       <c r="G7">
-        <v>28.7</v>
+        <v>28.3</v>
       </c>
       <c r="H7">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
       <c r="I7">
-        <v>12.3</v>
+        <v>14.1</v>
       </c>
       <c r="J7">
-        <v>61.8</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -1650,25 +1714,25 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="E8">
-        <v>11.5</v>
+        <v>3.2</v>
       </c>
       <c r="F8">
-        <v>22.1</v>
+        <v>16.9</v>
       </c>
       <c r="G8">
-        <v>23.2</v>
+        <v>24.8</v>
       </c>
       <c r="H8">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I8">
-        <v>16</v>
+        <v>19.8</v>
       </c>
       <c r="J8">
-        <v>58</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1685,22 +1749,22 @@
         <v>0.1</v>
       </c>
       <c r="E9">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="F9">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="G9">
-        <v>13.3</v>
+        <v>12.4</v>
       </c>
       <c r="H9">
-        <v>18.9</v>
+        <v>21.6</v>
       </c>
       <c r="I9">
-        <v>60</v>
+        <v>60.5</v>
       </c>
       <c r="J9">
-        <v>21.1</v>
+        <v>17.9</v>
       </c>
     </row>
   </sheetData>
@@ -1710,32 +1774,35 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>33</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>39.90000000000001</v>
+        <v>38.4</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -1749,36 +1816,42 @@
       <c r="F2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>98.8</v>
+        <v>100</v>
       </c>
       <c r="C3">
-        <v>98.59999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D3">
         <v>100</v>
       </c>
       <c r="E3">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
       <c r="F3">
-        <v>99.8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="G3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="C4">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="D4">
         <v>100</v>
@@ -1787,10 +1860,13 @@
         <v>99.90000000000001</v>
       </c>
       <c r="F4">
-        <v>99.7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="G4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -1798,96 +1874,111 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>94.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="D5">
         <v>99.8</v>
       </c>
       <c r="E5">
-        <v>93.89999999999999</v>
+        <v>93.60000000000001</v>
       </c>
       <c r="F5">
-        <v>93.10000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="G5">
+        <v>98.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>96</v>
+      </c>
+      <c r="C6">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="D6">
+        <v>31.6</v>
+      </c>
+      <c r="E6">
+        <v>58.8</v>
+      </c>
+      <c r="F6">
+        <v>80.30000000000001</v>
+      </c>
+      <c r="G6">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>88.8</v>
+      </c>
+      <c r="C7">
+        <v>34.4</v>
+      </c>
+      <c r="D7">
+        <v>25.6</v>
+      </c>
+      <c r="E7">
+        <v>57.49999999999999</v>
+      </c>
+      <c r="F7">
+        <v>56.59999999999999</v>
+      </c>
+      <c r="G7">
+        <v>58.09999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>90.10000000000001</v>
-      </c>
-      <c r="C6">
-        <v>12.4</v>
-      </c>
-      <c r="D6">
-        <v>92.60000000000001</v>
-      </c>
-      <c r="E6">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="F6">
-        <v>67.90000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7">
-        <v>96.89999999999999</v>
-      </c>
-      <c r="C7">
-        <v>64.2</v>
-      </c>
-      <c r="D7">
-        <v>34.5</v>
-      </c>
-      <c r="E7">
-        <v>56.89999999999999</v>
-      </c>
-      <c r="F7">
-        <v>60.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="B8">
-        <v>85.90000000000001</v>
+        <v>91.10000000000001</v>
       </c>
       <c r="C8">
-        <v>34.9</v>
+        <v>12.5</v>
       </c>
       <c r="D8">
-        <v>24.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="E8">
-        <v>59</v>
+        <v>72.3</v>
       </c>
       <c r="F8">
-        <v>59.59999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>48.5</v>
+      </c>
+      <c r="G8">
+        <v>47.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B9">
-        <v>88.40000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="C9">
-        <v>95.3</v>
+        <v>96.8</v>
       </c>
       <c r="D9">
         <v>48.9</v>
       </c>
       <c r="E9">
-        <v>16.6</v>
+        <v>18.2</v>
       </c>
       <c r="F9">
-        <v>19.7</v>
+        <v>15.9</v>
+      </c>
+      <c r="G9">
+        <v>16.9</v>
       </c>
     </row>
   </sheetData>
@@ -1902,28 +1993,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1931,28 +2022,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2">
-        <v>139.09</v>
+        <v>127.34</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>142.52</v>
+        <v>145.66</v>
       </c>
       <c r="G2">
-        <v>0.556</v>
+        <v>0.55</v>
       </c>
       <c r="H2">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1960,28 +2051,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D3">
-        <v>125.65</v>
+        <v>144.03</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>143.26</v>
+        <v>143.82</v>
       </c>
       <c r="G3">
-        <v>0.528</v>
+        <v>0.5</v>
       </c>
       <c r="H3">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1989,28 +2080,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D4">
-        <v>126.32</v>
+        <v>132.42</v>
       </c>
       <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4">
+        <v>143.9</v>
+      </c>
+      <c r="G4">
+        <v>0.575</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
         <v>8</v>
-      </c>
-      <c r="F4">
-        <v>142.26</v>
-      </c>
-      <c r="G4">
-        <v>0.528</v>
-      </c>
-      <c r="H4">
-        <v>1.6</v>
-      </c>
-      <c r="I4">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2021,25 +2112,25 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D5">
-        <v>131.27</v>
+        <v>133.17</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5">
-        <v>141.88</v>
+        <v>141.22</v>
       </c>
       <c r="G5">
-        <v>0.528</v>
+        <v>0.475</v>
       </c>
       <c r="H5">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2047,28 +2138,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D6">
-        <v>146.32</v>
+        <v>128.8</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>138.4</v>
+        <v>142.32</v>
       </c>
       <c r="G6">
-        <v>0.417</v>
+        <v>0.525</v>
       </c>
       <c r="H6">
-        <v>-0.8</v>
+        <v>-0.1</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2076,28 +2167,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D7">
-        <v>133.12</v>
+        <v>149.49</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>139.84</v>
+        <v>139.64</v>
       </c>
       <c r="G7">
-        <v>0.583</v>
+        <v>0.425</v>
       </c>
       <c r="H7">
         <v>-1.8</v>
       </c>
       <c r="I7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2105,28 +2196,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8">
-        <v>162.16</v>
+        <v>160.46</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F8">
-        <v>134.94</v>
+        <v>139.72</v>
       </c>
       <c r="G8">
-        <v>0.417</v>
+        <v>0.5</v>
       </c>
       <c r="H8">
-        <v>-2.4</v>
+        <v>-2.1</v>
       </c>
       <c r="I8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2134,28 +2225,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D9">
-        <v>155.74</v>
+        <v>158.44</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>136.59</v>
+        <v>137.88</v>
       </c>
       <c r="G9">
-        <v>0.444</v>
+        <v>0.45</v>
       </c>
       <c r="H9">
-        <v>-2.8</v>
+        <v>-3.1</v>
       </c>
       <c r="I9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2170,31 +2261,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2202,16 +2293,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>162.165</v>
+        <v>158.44</v>
       </c>
       <c r="E2">
-        <v>648.66</v>
+        <v>792.1999999999999</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2220,10 +2311,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2231,16 +2322,16 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D3">
-        <v>146.325</v>
+        <v>149.492</v>
       </c>
       <c r="E3">
-        <v>585.3</v>
+        <v>747.4599999999999</v>
       </c>
       <c r="F3">
         <v>100</v>
@@ -2249,10 +2340,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2260,28 +2351,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C4">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D4">
-        <v>155.735</v>
+        <v>160.464</v>
       </c>
       <c r="E4">
-        <v>622.9400000000001</v>
+        <v>802.3200000000001</v>
       </c>
       <c r="F4">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2289,115 +2380,115 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D5">
-        <v>139.095</v>
+        <v>144.032</v>
       </c>
       <c r="E5">
-        <v>556.38</v>
+        <v>720.16</v>
       </c>
       <c r="F5">
-        <v>90.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="G5">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C6">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="D6">
-        <v>133.12</v>
+        <v>127.344</v>
       </c>
       <c r="E6">
-        <v>532.48</v>
+        <v>636.72</v>
       </c>
       <c r="F6">
-        <v>68.7</v>
+        <v>79.5</v>
       </c>
       <c r="G6">
-        <v>9.199999999999999</v>
+        <v>5.600000000000001</v>
       </c>
       <c r="H6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="D7">
-        <v>125.645</v>
+        <v>133.172</v>
       </c>
       <c r="E7">
-        <v>502.58</v>
+        <v>665.8600000000001</v>
       </c>
       <c r="F7">
-        <v>61.8</v>
+        <v>59</v>
       </c>
       <c r="G7">
-        <v>12.3</v>
+        <v>14.1</v>
       </c>
       <c r="H7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C8">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D8">
-        <v>131.265</v>
+        <v>132.424</v>
       </c>
       <c r="E8">
-        <v>525.0600000000001</v>
+        <v>662.12</v>
       </c>
       <c r="F8">
-        <v>57.99999999999999</v>
+        <v>45.2</v>
       </c>
       <c r="G8">
-        <v>16</v>
+        <v>19.8</v>
       </c>
       <c r="H8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2405,28 +2496,28 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>126.32</v>
+        <v>128.8</v>
       </c>
       <c r="E9">
-        <v>505.28</v>
+        <v>644</v>
       </c>
       <c r="F9">
-        <v>21.1</v>
+        <v>17.9</v>
       </c>
       <c r="G9">
-        <v>60</v>
+        <v>60.5</v>
       </c>
       <c r="H9" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2441,19 +2532,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2464,16 +2555,16 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2481,19 +2572,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2501,10 +2592,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -2513,7 +2604,7 @@
         <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2521,19 +2612,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2544,16 +2635,16 @@
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D6">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2564,16 +2655,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D7">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2581,19 +2672,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D8">
         <v>-6</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2604,16 +2695,16 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9">
-        <v>-15</v>
+        <v>-22</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -2623,27 +2714,30 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>90</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -2659,71 +2753,83 @@
       <c r="E2">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="F2">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>4</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>9</v>
+      </c>
+      <c r="G3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>-8</v>
+      </c>
+      <c r="C4">
+        <v>-6</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
         <v>3</v>
       </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-      <c r="F4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B5">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="C5">
+        <v>-3</v>
+      </c>
+      <c r="D5">
+        <v>-2</v>
+      </c>
+      <c r="E5">
         <v>-6</v>
       </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -2739,11 +2845,14 @@
       <c r="E6">
         <v>-3</v>
       </c>
-      <c r="F6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="F6">
+        <v>-2</v>
+      </c>
+      <c r="G6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -2759,31 +2868,37 @@
       <c r="E7">
         <v>-3</v>
       </c>
-      <c r="F7" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="F7">
+        <v>-4</v>
+      </c>
+      <c r="G7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8">
-        <v>-10</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="D8">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
         <v>-6</v>
       </c>
-      <c r="F8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -2799,8 +2914,11 @@
       <c r="E9">
         <v>-15</v>
       </c>
-      <c r="F9" t="s">
-        <v>79</v>
+      <c r="F9">
+        <v>-22</v>
+      </c>
+      <c r="G9" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Ross' Fantasy League 2026.xlsx
+++ b/data/leagues/Ross' Fantasy League 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="99">
   <si>
     <t>Ross' Sauces</t>
   </si>
@@ -49,22 +49,22 @@
     <t>Yung Killas</t>
   </si>
   <si>
-    <t>0-5-0</t>
-  </si>
-  <si>
-    <t>3-2-0</t>
-  </si>
-  <si>
-    <t>2-3-0</t>
-  </si>
-  <si>
-    <t>1-4-0</t>
-  </si>
-  <si>
-    <t>5-0-0</t>
-  </si>
-  <si>
-    <t>4-1-0</t>
+    <t>1-5-0</t>
+  </si>
+  <si>
+    <t>4-2-0</t>
+  </si>
+  <si>
+    <t>3-3-0</t>
+  </si>
+  <si>
+    <t>2-4-0</t>
+  </si>
+  <si>
+    <t>5-1-0</t>
+  </si>
+  <si>
+    <t>0-6-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -130,6 +130,9 @@
     <t>Week_6</t>
   </si>
   <si>
+    <t>Week_7</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -154,27 +157,27 @@
     <t>Basak Gafoor</t>
   </si>
   <si>
+    <t>Nach Konuganti</t>
+  </si>
+  <si>
+    <t>William Le</t>
+  </si>
+  <si>
     <t>Michael Nader</t>
   </si>
   <si>
-    <t>Nach Konuganti</t>
-  </si>
-  <si>
-    <t>William Le</t>
-  </si>
-  <si>
     <t>Andrew Ross</t>
   </si>
   <si>
     <t>Tyler Rahman</t>
   </si>
   <si>
+    <t>Jackson Jansorn</t>
+  </si>
+  <si>
     <t>Alan Devera</t>
   </si>
   <si>
-    <t>Jackson Jansorn</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -199,49 +202,49 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>5-0</t>
-  </si>
-  <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>0-5</t>
-  </si>
-  <si>
-    <t>10.7-2.2-0.1</t>
-  </si>
-  <si>
-    <t>9.1-3.8-0.1</t>
-  </si>
-  <si>
-    <t>8.7-4.2-0.1</t>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>9.9-3.1-0.1</t>
+  </si>
+  <si>
+    <t>8.0-5.0-0.1</t>
+  </si>
+  <si>
+    <t>7.9-5.0-0.1</t>
+  </si>
+  <si>
+    <t>7.1-5.9-0.1</t>
   </si>
   <si>
     <t>6.9-6.0-0.1</t>
   </si>
   <si>
-    <t>5.3-7.6-0.1</t>
-  </si>
-  <si>
-    <t>4.3-8.6-0.1</t>
-  </si>
-  <si>
-    <t>3.8-9.1-0.1</t>
-  </si>
-  <si>
-    <t>2.8-10.2-0.1</t>
-  </si>
-  <si>
-    <t>11-2</t>
-  </si>
-  <si>
-    <t>9-4</t>
+    <t>4.7-8.3-0.1</t>
+  </si>
+  <si>
+    <t>4.1-8.9-0.1</t>
+  </si>
+  <si>
+    <t>3.3-9.7-0.1</t>
+  </si>
+  <si>
+    <t>10-3</t>
+  </si>
+  <si>
+    <t>8-5</t>
   </si>
   <si>
     <t>7-6</t>
@@ -265,22 +268,19 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑5</t>
-  </si>
-  <si>
-    <t>↑1</t>
-  </si>
-  <si>
-    <t>↑8</t>
-  </si>
-  <si>
-    <t>↓1</t>
-  </si>
-  <si>
-    <t>↓10</t>
-  </si>
-  <si>
-    <t>↓7</t>
+    <t>↓5</t>
+  </si>
+  <si>
+    <t>↑4</t>
+  </si>
+  <si>
+    <t>↓2</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>↑6</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -296,6 +296,9 @@
   </si>
   <si>
     <t>Week 5</t>
+  </si>
+  <si>
+    <t>Week 6</t>
   </si>
   <si>
     <t>Week</t>
@@ -720,7 +723,7 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
@@ -743,19 +746,19 @@
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G3" t="s">
         <v>9</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I3" t="s">
         <v>9</v>
@@ -766,28 +769,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -798,22 +801,22 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I5" t="s">
         <v>9</v>
@@ -842,7 +845,7 @@
         <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6" t="s">
         <v>10</v>
@@ -856,22 +859,22 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7" t="s">
         <v>11</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I7" t="s">
         <v>10</v>
@@ -882,25 +885,25 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
         <v>11</v>
       </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" t="s">
         <v>10</v>
       </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" t="s">
-        <v>9</v>
-      </c>
       <c r="H8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I8" t="s">
         <v>10</v>
@@ -914,7 +917,7 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -929,7 +932,7 @@
         <v>10</v>
       </c>
       <c r="H9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I9" t="s">
         <v>9</v>
@@ -942,30 +945,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -973,22 +976,22 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>-22</v>
+        <v>-16</v>
       </c>
       <c r="F2">
-        <v>-6</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
         <v>4</v>
@@ -999,25 +1002,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>-22</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="G3">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1025,25 +1028,25 @@
         <v>2</v>
       </c>
       <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
         <v>2</v>
       </c>
-      <c r="C4" t="s">
-        <v>1</v>
-      </c>
       <c r="D4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E4">
-        <v>-6</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1051,25 +1054,25 @@
         <v>3</v>
       </c>
       <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
         <v>3</v>
       </c>
-      <c r="C5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>2</v>
-      </c>
       <c r="E5">
-        <v>4</v>
+        <v>-8</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H5" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1077,25 +1080,25 @@
         <v>4</v>
       </c>
       <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
         <v>2</v>
       </c>
-      <c r="C6" t="s">
-        <v>0</v>
-      </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F6">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1103,25 +1106,25 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>-15</v>
+        <v>14</v>
       </c>
       <c r="G7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H7" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1129,25 +1132,25 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
       </c>
       <c r="E8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="F8">
         <v>4</v>
       </c>
       <c r="G8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H8" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1155,24 +1158,102 @@
         <v>7</v>
       </c>
       <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9">
+        <v>6</v>
+      </c>
+      <c r="F9">
+        <v>-3</v>
+      </c>
+      <c r="G9">
+        <v>9</v>
+      </c>
+      <c r="H9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <v>-6</v>
+      </c>
+      <c r="F10">
+        <v>-15</v>
+      </c>
+      <c r="G10">
+        <v>9</v>
+      </c>
+      <c r="H10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s">
         <v>5</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E11">
+        <v>-3</v>
+      </c>
+      <c r="F11">
+        <v>4</v>
+      </c>
+      <c r="G11">
+        <v>7</v>
+      </c>
+      <c r="H11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
         <v>3</v>
       </c>
-      <c r="D9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9">
-        <v>9</v>
-      </c>
-      <c r="F9">
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12">
+        <v>9</v>
+      </c>
+      <c r="F12">
         <v>2</v>
       </c>
-      <c r="G9">
-        <v>7</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="G12">
+        <v>7</v>
+      </c>
+      <c r="H12" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1205,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1.625</v>
+        <v>2.375</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -1219,10 +1300,10 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>2.375</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1233,7 +1314,7 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>2.625</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -1244,13 +1325,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>2.375</v>
+        <v>2.625</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1258,13 +1339,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1272,13 +1353,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>2.75</v>
+        <v>3.375</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1286,13 +1367,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>3.125</v>
+        <v>3.375</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1303,7 +1384,7 @@
         <v>4</v>
       </c>
       <c r="C9">
-        <v>3.625</v>
+        <v>4</v>
       </c>
       <c r="D9" t="s">
         <v>9</v>
@@ -1338,16 +1419,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>3.625</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>0.625</v>
+        <v>-1</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1355,16 +1436,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="D3">
-        <v>-1.5</v>
+        <v>-0.25</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1372,16 +1453,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>3.5</v>
+        <v>3.625</v>
       </c>
       <c r="D4">
-        <v>-0.5</v>
+        <v>0.625</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1392,10 +1473,10 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="D5">
-        <v>-0.5</v>
+        <v>-0.75</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1406,16 +1487,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>2.125</v>
+        <v>2.625</v>
       </c>
       <c r="D6">
-        <v>1.125</v>
+        <v>-1.375</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1423,16 +1504,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="D7">
-        <v>-1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1440,16 +1521,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="D8">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1457,16 +1538,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
         <v>0</v>
       </c>
-      <c r="C9">
-        <v>1.5</v>
-      </c>
-      <c r="D9">
-        <v>1.5</v>
-      </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1516,19 +1597,19 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>68.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="C2">
-        <v>23.2</v>
+        <v>14</v>
       </c>
       <c r="D2">
-        <v>7.3</v>
+        <v>5.4</v>
       </c>
       <c r="E2">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1548,95 +1629,95 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>13.9</v>
+        <v>8.5</v>
       </c>
       <c r="C3">
-        <v>35.4</v>
+        <v>28.5</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>27.8</v>
       </c>
       <c r="E3">
-        <v>11.7</v>
+        <v>21.8</v>
       </c>
       <c r="F3">
-        <v>0.7</v>
+        <v>10.9</v>
       </c>
       <c r="G3">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>15.9</v>
+        <v>7.5</v>
       </c>
       <c r="C4">
-        <v>36.5</v>
+        <v>29.2</v>
       </c>
       <c r="D4">
-        <v>34.8</v>
+        <v>28.3</v>
       </c>
       <c r="E4">
-        <v>10.7</v>
+        <v>19.4</v>
       </c>
       <c r="F4">
-        <v>1.9</v>
+        <v>11.7</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J4">
-        <v>99.8</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B5">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="C5">
-        <v>4.6</v>
+        <v>19.9</v>
       </c>
       <c r="D5">
-        <v>17.3</v>
+        <v>21.2</v>
       </c>
       <c r="E5">
-        <v>56</v>
+        <v>26.7</v>
       </c>
       <c r="F5">
-        <v>14.1</v>
+        <v>19.7</v>
       </c>
       <c r="G5">
-        <v>5.4</v>
+        <v>6.3</v>
       </c>
       <c r="H5">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="J5">
-        <v>98.59999999999999</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1644,36 +1725,36 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0.1</v>
+        <v>1.7</v>
       </c>
       <c r="C6">
-        <v>0.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D6">
-        <v>1.8</v>
+        <v>15.2</v>
       </c>
       <c r="E6">
-        <v>11.1</v>
+        <v>22.7</v>
       </c>
       <c r="F6">
-        <v>37.5</v>
+        <v>34.6</v>
       </c>
       <c r="G6">
-        <v>28.8</v>
+        <v>12.6</v>
       </c>
       <c r="H6">
-        <v>14.9</v>
+        <v>3.9</v>
       </c>
       <c r="I6">
-        <v>5.6</v>
+        <v>1.1</v>
       </c>
       <c r="J6">
-        <v>79.5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1682,62 +1763,62 @@
         <v>0.1</v>
       </c>
       <c r="D7">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>24.2</v>
+        <v>11.8</v>
       </c>
       <c r="G7">
-        <v>28.3</v>
+        <v>35.8</v>
       </c>
       <c r="H7">
-        <v>26.9</v>
+        <v>31.9</v>
       </c>
       <c r="I7">
-        <v>14.1</v>
+        <v>15.4</v>
       </c>
       <c r="J7">
-        <v>59</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D8">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="E8">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="F8">
-        <v>16.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G8">
-        <v>24.8</v>
+        <v>30.5</v>
       </c>
       <c r="H8">
-        <v>35</v>
+        <v>34.7</v>
       </c>
       <c r="I8">
-        <v>19.8</v>
+        <v>22.4</v>
       </c>
       <c r="J8">
-        <v>45.2</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1746,25 +1827,25 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E9">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F9">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="G9">
-        <v>12.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H9">
-        <v>21.6</v>
+        <v>27</v>
       </c>
       <c r="I9">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
       <c r="J9">
-        <v>17.9</v>
+        <v>12.7</v>
       </c>
     </row>
   </sheetData>
@@ -1774,10 +1855,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
@@ -1796,13 +1877,16 @@
       <c r="G1" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>38.4</v>
+        <v>41.2</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -1819,166 +1903,190 @@
       <c r="G2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>99.90000000000001</v>
+        <v>93.89999999999999</v>
       </c>
       <c r="D3">
-        <v>100</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E3">
+        <v>91.60000000000001</v>
+      </c>
+      <c r="F3">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="G3">
         <v>99.7</v>
       </c>
-      <c r="F3">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="G3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="H3">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>98.5</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="C4">
-        <v>98.5</v>
+        <v>97.89999999999999</v>
       </c>
       <c r="D4">
         <v>100</v>
       </c>
       <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="G4">
         <v>99.90000000000001</v>
       </c>
-      <c r="F4">
+      <c r="H4">
+        <v>99.40000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>100</v>
+      </c>
+      <c r="C5">
         <v>99.90000000000001</v>
       </c>
-      <c r="G4">
+      <c r="D5">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
+      <c r="E5">
+        <v>99.8</v>
+      </c>
+      <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5">
+        <v>97.89999999999999</v>
+      </c>
+      <c r="H5">
+        <v>98.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>96.3</v>
+      </c>
+      <c r="C6">
+        <v>63.6</v>
+      </c>
+      <c r="D6">
+        <v>31.3</v>
+      </c>
+      <c r="E6">
+        <v>59.8</v>
+      </c>
+      <c r="F6">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="G6">
+        <v>92.2</v>
+      </c>
+      <c r="H6">
+        <v>93.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>89</v>
+      </c>
+      <c r="C7">
+        <v>11.4</v>
+      </c>
+      <c r="D7">
+        <v>94.19999999999999</v>
+      </c>
+      <c r="E7">
+        <v>70.3</v>
+      </c>
+      <c r="F7">
+        <v>52.3</v>
+      </c>
+      <c r="G7">
+        <v>47.59999999999999</v>
+      </c>
+      <c r="H7">
+        <v>54.40000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C5">
-        <v>93.5</v>
-      </c>
-      <c r="D5">
-        <v>99.8</v>
-      </c>
-      <c r="E5">
-        <v>93.60000000000001</v>
-      </c>
-      <c r="F5">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="G5">
-        <v>98.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>96</v>
-      </c>
-      <c r="C6">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="D6">
-        <v>31.6</v>
-      </c>
-      <c r="E6">
-        <v>58.8</v>
-      </c>
-      <c r="F6">
-        <v>80.30000000000001</v>
-      </c>
-      <c r="G6">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>88.8</v>
-      </c>
-      <c r="C7">
-        <v>34.4</v>
-      </c>
-      <c r="D7">
-        <v>25.6</v>
-      </c>
-      <c r="E7">
-        <v>57.49999999999999</v>
-      </c>
-      <c r="F7">
-        <v>56.59999999999999</v>
-      </c>
-      <c r="G7">
-        <v>58.09999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="B8">
-        <v>91.10000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="C8">
-        <v>12.5</v>
+        <v>95.8</v>
       </c>
       <c r="D8">
-        <v>94.09999999999999</v>
+        <v>51.2</v>
       </c>
       <c r="E8">
-        <v>72.3</v>
+        <v>16.2</v>
       </c>
       <c r="F8">
-        <v>48.5</v>
+        <v>15.3</v>
       </c>
       <c r="G8">
         <v>47.3</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="H8">
+        <v>39.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B9">
-        <v>87.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="C9">
-        <v>96.8</v>
+        <v>37.5</v>
       </c>
       <c r="D9">
-        <v>48.9</v>
+        <v>23.7</v>
       </c>
       <c r="E9">
-        <v>18.2</v>
+        <v>62.3</v>
       </c>
       <c r="F9">
-        <v>15.9</v>
+        <v>55.40000000000001</v>
       </c>
       <c r="G9">
-        <v>16.9</v>
+        <v>15.4</v>
+      </c>
+      <c r="H9">
+        <v>15.4</v>
       </c>
     </row>
   </sheetData>
@@ -1996,25 +2104,25 @@
         <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2025,25 +2133,25 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2">
-        <v>127.34</v>
+        <v>132.23</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2">
-        <v>145.66</v>
+        <v>139.96</v>
       </c>
       <c r="G2">
-        <v>0.55</v>
+        <v>0.476</v>
       </c>
       <c r="H2">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2051,28 +2159,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3">
-        <v>144.03</v>
+        <v>130.6</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>143.82</v>
+        <v>140.19</v>
       </c>
       <c r="G3">
-        <v>0.5</v>
+        <v>0.524</v>
       </c>
       <c r="H3">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2080,28 +2188,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4">
-        <v>132.42</v>
+        <v>125.74</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>143.9</v>
+        <v>140.88</v>
       </c>
       <c r="G4">
-        <v>0.575</v>
+        <v>0.548</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2109,28 +2217,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D5">
-        <v>133.17</v>
+        <v>143.45</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>141.22</v>
+        <v>138.35</v>
       </c>
       <c r="G5">
-        <v>0.475</v>
+        <v>0.476</v>
       </c>
       <c r="H5">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2141,25 +2249,25 @@
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6">
-        <v>128.8</v>
+        <v>134.1</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6">
-        <v>142.32</v>
+        <v>139.69</v>
       </c>
       <c r="G6">
-        <v>0.525</v>
+        <v>0.548</v>
       </c>
       <c r="H6">
         <v>-0.1</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2170,25 +2278,25 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7">
-        <v>149.49</v>
+        <v>144.01</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F7">
-        <v>139.64</v>
+        <v>138.27</v>
       </c>
       <c r="G7">
-        <v>0.425</v>
+        <v>0.476</v>
       </c>
       <c r="H7">
-        <v>-1.8</v>
+        <v>-0.4</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2196,28 +2304,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8">
-        <v>160.46</v>
+        <v>154.19</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>139.72</v>
+        <v>136.82</v>
       </c>
       <c r="G8">
-        <v>0.5</v>
+        <v>0.452</v>
       </c>
       <c r="H8">
-        <v>-2.1</v>
+        <v>-1</v>
       </c>
       <c r="I8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2225,28 +2333,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D9">
-        <v>158.44</v>
+        <v>147.61</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>137.88</v>
+        <v>137.76</v>
       </c>
       <c r="G9">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="H9">
-        <v>-3.1</v>
+        <v>-2</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2264,28 +2372,28 @@
         <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2293,16 +2401,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D2">
-        <v>158.44</v>
+        <v>154.1866666666666</v>
       </c>
       <c r="E2">
-        <v>792.1999999999999</v>
+        <v>925.1199999999999</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2311,10 +2419,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2322,86 +2430,86 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C3">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D3">
-        <v>149.492</v>
+        <v>144.01</v>
       </c>
       <c r="E3">
-        <v>747.4599999999999</v>
+        <v>864.0599999999999</v>
       </c>
       <c r="F3">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
       </c>
       <c r="C4">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D4">
-        <v>160.464</v>
+        <v>143.45</v>
       </c>
       <c r="E4">
-        <v>802.3200000000001</v>
+        <v>860.6999999999999</v>
       </c>
       <c r="F4">
-        <v>99.8</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D5">
-        <v>144.032</v>
+        <v>147.6133333333333</v>
       </c>
       <c r="E5">
-        <v>720.16</v>
+        <v>885.6800000000001</v>
       </c>
       <c r="F5">
-        <v>98.59999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2412,22 +2520,22 @@
         <v>60</v>
       </c>
       <c r="C6">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D6">
-        <v>127.344</v>
+        <v>132.2266666666667</v>
       </c>
       <c r="E6">
-        <v>636.72</v>
+        <v>793.36</v>
       </c>
       <c r="F6">
-        <v>79.5</v>
+        <v>95</v>
       </c>
       <c r="G6">
-        <v>5.600000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="H6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I6" t="s">
         <v>74</v>
@@ -2435,28 +2543,28 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C7">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D7">
-        <v>133.172</v>
+        <v>130.6033333333333</v>
       </c>
       <c r="E7">
-        <v>665.8600000000001</v>
+        <v>783.62</v>
       </c>
       <c r="F7">
-        <v>59</v>
+        <v>52.7</v>
       </c>
       <c r="G7">
-        <v>14.1</v>
+        <v>15.4</v>
       </c>
       <c r="H7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I7" t="s">
         <v>75</v>
@@ -2464,60 +2572,60 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C8">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D8">
-        <v>132.424</v>
+        <v>134.0966666666667</v>
       </c>
       <c r="E8">
-        <v>662.12</v>
+        <v>804.58</v>
       </c>
       <c r="F8">
-        <v>45.2</v>
+        <v>42.9</v>
       </c>
       <c r="G8">
-        <v>19.8</v>
+        <v>22.4</v>
       </c>
       <c r="H8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D9">
-        <v>128.8</v>
+        <v>125.7433333333334</v>
       </c>
       <c r="E9">
-        <v>644</v>
+        <v>754.4600000000002</v>
       </c>
       <c r="F9">
-        <v>17.9</v>
+        <v>12.7</v>
       </c>
       <c r="G9">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
       <c r="H9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -2535,16 +2643,16 @@
         <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2555,16 +2663,16 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2572,19 +2680,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2592,16 +2700,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4">
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
         <v>81</v>
@@ -2612,16 +2720,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
         <v>82</v>
@@ -2632,19 +2740,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
         <v>46</v>
       </c>
       <c r="D6">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2661,10 +2769,10 @@
         <v>-4</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2678,13 +2786,13 @@
         <v>44</v>
       </c>
       <c r="D8">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2695,10 +2803,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D9">
-        <v>-22</v>
+        <v>-16</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -2714,10 +2822,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
         <v>86</v>
       </c>
@@ -2734,10 +2842,13 @@
         <v>90</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>91</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -2756,103 +2867,118 @@
       <c r="F2">
         <v>20</v>
       </c>
-      <c r="G2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="G2">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>-8</v>
+      </c>
+      <c r="C3">
+        <v>-6</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
         <v>0</v>
       </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>-8</v>
-      </c>
-      <c r="C4">
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>-3</v>
+      </c>
+      <c r="F5">
+        <v>-2</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>-10</v>
+      </c>
+      <c r="C6">
+        <v>-3</v>
+      </c>
+      <c r="D6">
+        <v>-2</v>
+      </c>
+      <c r="E6">
         <v>-6</v>
       </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>4</v>
-      </c>
-      <c r="G4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
-        <v>-10</v>
-      </c>
-      <c r="C5">
-        <v>-3</v>
-      </c>
-      <c r="D5">
-        <v>-2</v>
-      </c>
-      <c r="E5">
-        <v>-6</v>
-      </c>
-      <c r="F5">
+      <c r="F6">
         <v>2</v>
       </c>
-      <c r="G5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
+      <c r="G6">
         <v>0</v>
       </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>-3</v>
-      </c>
-      <c r="F6">
-        <v>-2</v>
-      </c>
-      <c r="G6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="H6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -2871,11 +2997,14 @@
       <c r="F7">
         <v>-4</v>
       </c>
-      <c r="G7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="G7">
+        <v>-4</v>
+      </c>
+      <c r="H7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -2894,11 +3023,14 @@
       <c r="F8">
         <v>-6</v>
       </c>
-      <c r="G8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="G8">
+        <v>-8</v>
+      </c>
+      <c r="H8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -2917,7 +3049,10 @@
       <c r="F9">
         <v>-22</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9">
+        <v>-16</v>
+      </c>
+      <c r="H9" t="s">
         <v>85</v>
       </c>
     </row>

--- a/data/leagues/Ross' Fantasy League 2026.xlsx
+++ b/data/leagues/Ross' Fantasy League 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="102">
   <si>
     <t>Ross' Sauces</t>
   </si>
@@ -49,22 +49,22 @@
     <t>Yung Killas</t>
   </si>
   <si>
-    <t>1-5-0</t>
-  </si>
-  <si>
-    <t>4-2-0</t>
-  </si>
-  <si>
-    <t>3-3-0</t>
-  </si>
-  <si>
-    <t>2-4-0</t>
-  </si>
-  <si>
-    <t>5-1-0</t>
-  </si>
-  <si>
-    <t>0-6-0</t>
+    <t>2-5-0</t>
+  </si>
+  <si>
+    <t>5-2-0</t>
+  </si>
+  <si>
+    <t>3-4-0</t>
+  </si>
+  <si>
+    <t>4-3-0</t>
+  </si>
+  <si>
+    <t>1-6-0</t>
+  </si>
+  <si>
+    <t>6-1-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -133,6 +133,9 @@
     <t>Week_7</t>
   </si>
   <si>
+    <t>Week_8</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -154,30 +157,30 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Andrew Ross</t>
+  </si>
+  <si>
     <t>Basak Gafoor</t>
   </si>
   <si>
     <t>Nach Konuganti</t>
   </si>
   <si>
+    <t>Michael Nader</t>
+  </si>
+  <si>
+    <t>Alan Devera</t>
+  </si>
+  <si>
     <t>William Le</t>
   </si>
   <si>
-    <t>Michael Nader</t>
-  </si>
-  <si>
-    <t>Andrew Ross</t>
+    <t>Jackson Jansorn</t>
   </si>
   <si>
     <t>Tyler Rahman</t>
   </si>
   <si>
-    <t>Jackson Jansorn</t>
-  </si>
-  <si>
-    <t>Alan Devera</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -202,63 +205,60 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>1-5</t>
-  </si>
-  <si>
-    <t>9.9-3.1-0.1</t>
-  </si>
-  <si>
-    <t>8.0-5.0-0.1</t>
-  </si>
-  <si>
-    <t>7.9-5.0-0.1</t>
-  </si>
-  <si>
-    <t>7.1-5.9-0.1</t>
-  </si>
-  <si>
-    <t>6.9-6.0-0.1</t>
-  </si>
-  <si>
-    <t>4.7-8.3-0.1</t>
-  </si>
-  <si>
-    <t>4.1-8.9-0.1</t>
-  </si>
-  <si>
-    <t>3.3-9.7-0.1</t>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>9.2-3.7-0.1</t>
+  </si>
+  <si>
+    <t>9.0-3.9-0.1</t>
+  </si>
+  <si>
+    <t>7.2-5.8-0.1</t>
+  </si>
+  <si>
+    <t>6.4-6.5-0.1</t>
+  </si>
+  <si>
+    <t>6.1-6.9-0.1</t>
+  </si>
+  <si>
+    <t>5.4-7.5-0.1</t>
+  </si>
+  <si>
+    <t>4.5-8.4-0.1</t>
+  </si>
+  <si>
+    <t>3.9-9.0-0.1</t>
   </si>
   <si>
     <t>10-3</t>
   </si>
   <si>
-    <t>8-5</t>
+    <t>9-4</t>
   </si>
   <si>
     <t>7-6</t>
   </si>
   <si>
+    <t>6-7</t>
+  </si>
+  <si>
     <t>5-8</t>
   </si>
   <si>
     <t>4-9</t>
   </si>
   <si>
-    <t>3-10</t>
-  </si>
-  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -268,19 +268,25 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↓5</t>
-  </si>
-  <si>
-    <t>↑4</t>
-  </si>
-  <si>
-    <t>↓2</t>
+    <t>↑7</t>
+  </si>
+  <si>
+    <t>↑11</t>
+  </si>
+  <si>
+    <t>↓11</t>
+  </si>
+  <si>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>↓3</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>↑6</t>
+    <t>↓8</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -299,6 +305,9 @@
   </si>
   <si>
     <t>Week 6</t>
+  </si>
+  <si>
+    <t>Week 7</t>
   </si>
   <si>
     <t>Week</t>
@@ -717,22 +726,22 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -743,13 +752,13 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
@@ -772,22 +781,22 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
       <c r="G4" t="s">
         <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I4" t="s">
         <v>10</v>
@@ -798,7 +807,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
@@ -810,10 +819,10 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H5" t="s">
         <v>9</v>
@@ -827,10 +836,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
         <v>11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
@@ -839,13 +848,13 @@
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I6" t="s">
         <v>10</v>
@@ -856,13 +865,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -871,13 +880,13 @@
         <v>10</v>
       </c>
       <c r="G7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
       </c>
       <c r="I7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -885,19 +894,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G8" t="s">
         <v>10</v>
@@ -917,25 +926,25 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
         <v>11</v>
       </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G9" t="s">
         <v>10</v>
       </c>
       <c r="H9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -945,30 +954,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1028,25 +1037,25 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
         <v>2</v>
       </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
       <c r="E4">
-        <v>15</v>
+        <v>-12</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1057,22 +1066,22 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>-8</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1080,25 +1089,25 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>-8</v>
       </c>
       <c r="F6">
         <v>4</v>
       </c>
       <c r="G6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1106,25 +1115,25 @@
         <v>5</v>
       </c>
       <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
         <v>3</v>
       </c>
-      <c r="C7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>2</v>
-      </c>
       <c r="E7">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H7" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1158,25 +1167,25 @@
         <v>7</v>
       </c>
       <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
         <v>2</v>
       </c>
-      <c r="C9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" t="s">
-        <v>7</v>
-      </c>
       <c r="E9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>-3</v>
+        <v>14</v>
       </c>
       <c r="G9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H9" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1210,25 +1219,25 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E11">
+        <v>6</v>
+      </c>
+      <c r="F11">
         <v>-3</v>
       </c>
-      <c r="F11">
-        <v>4</v>
-      </c>
       <c r="G11">
+        <v>9</v>
+      </c>
+      <c r="H11" t="s">
         <v>7</v>
-      </c>
-      <c r="H11" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1236,25 +1245,77 @@
         <v>10</v>
       </c>
       <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" t="s">
         <v>5</v>
       </c>
-      <c r="C12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" t="s">
-        <v>7</v>
-      </c>
       <c r="E12">
-        <v>9</v>
+        <v>-3</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G12">
         <v>7</v>
       </c>
       <c r="H12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" t="s">
         <v>7</v>
+      </c>
+      <c r="E13">
+        <v>9</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13">
+        <v>7</v>
+      </c>
+      <c r="H13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14">
+        <v>-3</v>
+      </c>
+      <c r="F14">
+        <v>-8</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+      <c r="H14" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1286,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>2.375</v>
+        <v>2.875</v>
       </c>
       <c r="D2" t="s">
         <v>8</v>
@@ -1300,7 +1361,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>2.375</v>
+        <v>3.25</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1314,10 +1375,10 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>2.625</v>
+        <v>3.25</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1325,13 +1386,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>2.625</v>
+        <v>3.5</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1339,10 +1400,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="D6" t="s">
         <v>9</v>
@@ -1353,13 +1414,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>3.375</v>
+        <v>3.5</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1367,13 +1428,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>3.375</v>
+        <v>3.75</v>
       </c>
       <c r="D8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1384,10 +1445,10 @@
         <v>4</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>4.375</v>
       </c>
       <c r="D9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1422,13 +1483,13 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="D2">
-        <v>-1</v>
+        <v>-0.25</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1439,7 +1500,7 @@
         <v>3</v>
       </c>
       <c r="C3">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="D3">
         <v>-0.25</v>
@@ -1473,13 +1534,13 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="D5">
-        <v>-0.75</v>
+        <v>-0.5</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1487,16 +1548,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>2.625</v>
+        <v>3.25</v>
       </c>
       <c r="D6">
-        <v>-1.375</v>
+        <v>1.25</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1504,16 +1565,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>1.5</v>
+        <v>-1</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1521,16 +1582,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>2.25</v>
+        <v>2.625</v>
       </c>
       <c r="D8">
-        <v>1.25</v>
+        <v>-0.375</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1538,16 +1599,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1597,22 +1658,22 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>78</v>
+        <v>60.3</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>30.6</v>
       </c>
       <c r="D2">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="E2">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="F2">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1629,31 +1690,31 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>8.5</v>
+        <v>35.3</v>
       </c>
       <c r="C3">
-        <v>28.5</v>
+        <v>49.4</v>
       </c>
       <c r="D3">
-        <v>27.8</v>
+        <v>11.2</v>
       </c>
       <c r="E3">
-        <v>21.8</v>
+        <v>3.2</v>
       </c>
       <c r="F3">
-        <v>10.9</v>
+        <v>0.7</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="H3">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>99.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1661,95 +1722,95 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="C4">
-        <v>29.2</v>
+        <v>11.5</v>
       </c>
       <c r="D4">
-        <v>28.3</v>
+        <v>40.2</v>
       </c>
       <c r="E4">
-        <v>19.4</v>
+        <v>24.4</v>
       </c>
       <c r="F4">
-        <v>11.7</v>
+        <v>13.8</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>5.9</v>
       </c>
       <c r="H4">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="I4">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J4">
-        <v>99.09999999999999</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="C5">
-        <v>19.9</v>
+        <v>2.7</v>
       </c>
       <c r="D5">
-        <v>21.2</v>
+        <v>14.6</v>
       </c>
       <c r="E5">
-        <v>26.7</v>
+        <v>24.5</v>
       </c>
       <c r="F5">
-        <v>19.7</v>
+        <v>27.5</v>
       </c>
       <c r="G5">
-        <v>6.3</v>
+        <v>19.4</v>
       </c>
       <c r="H5">
+        <v>8.9</v>
+      </c>
+      <c r="I5">
         <v>1.5</v>
       </c>
-      <c r="I5">
-        <v>0.4</v>
-      </c>
       <c r="J5">
-        <v>98.09999999999999</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B6">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="C6">
-        <v>8.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="D6">
+        <v>20.9</v>
+      </c>
+      <c r="E6">
+        <v>26.2</v>
+      </c>
+      <c r="F6">
+        <v>19</v>
+      </c>
+      <c r="G6">
         <v>15.2</v>
       </c>
-      <c r="E6">
-        <v>22.7</v>
-      </c>
-      <c r="F6">
-        <v>34.6</v>
-      </c>
-      <c r="G6">
-        <v>12.6</v>
-      </c>
       <c r="H6">
-        <v>3.9</v>
+        <v>10.3</v>
       </c>
       <c r="I6">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J6">
-        <v>95</v>
+        <v>87.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1760,28 +1821,28 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>12.7</v>
       </c>
       <c r="F7">
-        <v>11.8</v>
+        <v>19</v>
       </c>
       <c r="G7">
-        <v>35.8</v>
+        <v>27.1</v>
       </c>
       <c r="H7">
-        <v>31.9</v>
+        <v>25.1</v>
       </c>
       <c r="I7">
-        <v>15.4</v>
+        <v>11.9</v>
       </c>
       <c r="J7">
-        <v>52.7</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1792,28 +1853,28 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="D8">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="E8">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="F8">
-        <v>8.699999999999999</v>
+        <v>14</v>
       </c>
       <c r="G8">
-        <v>30.5</v>
+        <v>21.9</v>
       </c>
       <c r="H8">
-        <v>34.7</v>
+        <v>30.7</v>
       </c>
       <c r="I8">
-        <v>22.4</v>
+        <v>24.5</v>
       </c>
       <c r="J8">
-        <v>42.9</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1827,25 +1888,25 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E9">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F9">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="G9">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="H9">
-        <v>27</v>
+        <v>23.2</v>
       </c>
       <c r="I9">
-        <v>60.3</v>
+        <v>59.7</v>
       </c>
       <c r="J9">
-        <v>12.7</v>
+        <v>17.1</v>
       </c>
     </row>
   </sheetData>
@@ -1855,10 +1916,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
@@ -1880,16 +1941,19 @@
       <c r="H1" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>41.2</v>
+        <v>42.8</v>
       </c>
       <c r="C2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D2">
         <v>100</v>
@@ -1906,187 +1970,211 @@
       <c r="H2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>98.2</v>
+      </c>
+      <c r="C3">
+        <v>98</v>
+      </c>
+      <c r="D3">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="E3">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="F3">
+        <v>100</v>
+      </c>
+      <c r="G3">
+        <v>99.5</v>
+      </c>
+      <c r="H3">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I3">
+        <v>99.90000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>0</v>
       </c>
-      <c r="C3">
-        <v>93.89999999999999</v>
-      </c>
-      <c r="D3">
+      <c r="C4">
+        <v>94.3</v>
+      </c>
+      <c r="D4">
         <v>99.59999999999999</v>
       </c>
-      <c r="E3">
-        <v>91.60000000000001</v>
-      </c>
-      <c r="F3">
+      <c r="E4">
+        <v>93.10000000000001</v>
+      </c>
+      <c r="F4">
         <v>98.59999999999999</v>
       </c>
-      <c r="G3">
+      <c r="G4">
+        <v>99</v>
+      </c>
+      <c r="H4">
+        <v>97.39999999999999</v>
+      </c>
+      <c r="I4">
+        <v>97.89999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>96</v>
+      </c>
+      <c r="C5">
+        <v>64.7</v>
+      </c>
+      <c r="D5">
+        <v>33.3</v>
+      </c>
+      <c r="E5">
+        <v>59.9</v>
+      </c>
+      <c r="F5">
+        <v>80</v>
+      </c>
+      <c r="G5">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="H5">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="I5">
+        <v>90.40000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>100</v>
+      </c>
+      <c r="C6">
         <v>99.7</v>
       </c>
-      <c r="H3">
-        <v>99.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="C4">
-        <v>97.89999999999999</v>
-      </c>
-      <c r="D4">
+      <c r="D6">
         <v>100</v>
       </c>
-      <c r="E4">
-        <v>100</v>
-      </c>
-      <c r="F4">
-        <v>100</v>
-      </c>
-      <c r="G4">
+      <c r="E6">
+        <v>99.8</v>
+      </c>
+      <c r="F6">
         <v>99.90000000000001</v>
       </c>
-      <c r="H4">
-        <v>99.40000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>100</v>
-      </c>
-      <c r="C5">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="D5">
-        <v>100</v>
-      </c>
-      <c r="E5">
-        <v>99.8</v>
-      </c>
-      <c r="F5">
-        <v>100</v>
-      </c>
-      <c r="G5">
-        <v>97.89999999999999</v>
-      </c>
-      <c r="H5">
-        <v>98.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>96.3</v>
-      </c>
-      <c r="C6">
-        <v>63.6</v>
-      </c>
-      <c r="D6">
-        <v>31.3</v>
-      </c>
-      <c r="E6">
-        <v>59.8</v>
-      </c>
-      <c r="F6">
-        <v>78.40000000000001</v>
-      </c>
       <c r="G6">
-        <v>92.2</v>
+        <v>97.39999999999999</v>
       </c>
       <c r="H6">
-        <v>93.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>91.7</v>
+      </c>
+      <c r="I6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B7">
-        <v>89</v>
+        <v>89.8</v>
       </c>
       <c r="C7">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="D7">
-        <v>94.19999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="E7">
-        <v>70.3</v>
+        <v>71</v>
       </c>
       <c r="F7">
-        <v>52.3</v>
+        <v>50.5</v>
       </c>
       <c r="G7">
-        <v>47.59999999999999</v>
+        <v>47.2</v>
       </c>
       <c r="H7">
-        <v>54.40000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>57.2</v>
+      </c>
+      <c r="I7">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B8">
-        <v>88.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="C8">
-        <v>95.8</v>
+        <v>95.3</v>
       </c>
       <c r="D8">
-        <v>51.2</v>
+        <v>49.9</v>
       </c>
       <c r="E8">
-        <v>16.2</v>
+        <v>15.2</v>
       </c>
       <c r="F8">
-        <v>15.3</v>
+        <v>15.9</v>
       </c>
       <c r="G8">
-        <v>47.3</v>
+        <v>47</v>
       </c>
       <c r="H8">
-        <v>39.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>48.8</v>
+      </c>
+      <c r="I8">
+        <v>43.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B9">
-        <v>86.40000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="C9">
-        <v>37.5</v>
+        <v>36.5</v>
       </c>
       <c r="D9">
-        <v>23.7</v>
+        <v>24.1</v>
       </c>
       <c r="E9">
-        <v>62.3</v>
+        <v>61.1</v>
       </c>
       <c r="F9">
-        <v>55.40000000000001</v>
+        <v>55.1</v>
       </c>
       <c r="G9">
-        <v>15.4</v>
+        <v>17</v>
       </c>
       <c r="H9">
-        <v>15.4</v>
+        <v>16.1</v>
+      </c>
+      <c r="I9">
+        <v>15.8</v>
       </c>
     </row>
   </sheetData>
@@ -2104,25 +2192,25 @@
         <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2130,28 +2218,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2">
-        <v>132.23</v>
+        <v>134.41</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>139.96</v>
+        <v>140.37</v>
       </c>
       <c r="G2">
-        <v>0.476</v>
+        <v>0.524</v>
       </c>
       <c r="H2">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2159,28 +2247,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D3">
-        <v>130.6</v>
+        <v>132.33</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3">
-        <v>140.19</v>
+        <v>140.37</v>
       </c>
       <c r="G3">
         <v>0.524</v>
       </c>
       <c r="H3">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2188,28 +2276,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4">
-        <v>125.74</v>
+        <v>131.01</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>140.88</v>
+        <v>139.47</v>
       </c>
       <c r="G4">
-        <v>0.548</v>
+        <v>0.5</v>
       </c>
       <c r="H4">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2220,25 +2308,25 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D5">
-        <v>143.45</v>
+        <v>141.12</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>138.35</v>
+        <v>139.47</v>
       </c>
       <c r="G5">
-        <v>0.476</v>
+        <v>0.5</v>
       </c>
       <c r="H5">
-        <v>0.1</v>
+        <v>1.7</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2246,28 +2334,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D6">
-        <v>134.1</v>
+        <v>142.45</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>139.69</v>
+        <v>140.19</v>
       </c>
       <c r="G6">
         <v>0.548</v>
       </c>
       <c r="H6">
-        <v>-0.1</v>
+        <v>1.2</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2275,28 +2363,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7">
-        <v>144.01</v>
+        <v>125.35</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>138.27</v>
+        <v>140.19</v>
       </c>
       <c r="G7">
-        <v>0.476</v>
+        <v>0.548</v>
       </c>
       <c r="H7">
-        <v>-0.4</v>
+        <v>1.2</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2307,25 +2395,25 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8">
-        <v>154.19</v>
+        <v>153.57</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F8">
-        <v>136.82</v>
+        <v>134.45</v>
       </c>
       <c r="G8">
-        <v>0.452</v>
+        <v>0.429</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>-5.2</v>
       </c>
       <c r="I8">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2333,28 +2421,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9">
-        <v>147.61</v>
+        <v>148.72</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9">
-        <v>137.76</v>
+        <v>134.45</v>
       </c>
       <c r="G9">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="H9">
-        <v>-2</v>
+        <v>-5.2</v>
       </c>
       <c r="I9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2372,28 +2460,28 @@
         <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2401,16 +2489,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C2">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D2">
-        <v>154.1866666666666</v>
+        <v>153.5714285714286</v>
       </c>
       <c r="E2">
-        <v>925.1199999999999</v>
+        <v>1075</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2433,19 +2521,19 @@
         <v>60</v>
       </c>
       <c r="C3">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D3">
-        <v>144.01</v>
+        <v>148.72</v>
       </c>
       <c r="E3">
-        <v>864.0599999999999</v>
+        <v>1041.04</v>
       </c>
       <c r="F3">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="G3">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="s">
         <v>65</v>
@@ -2459,86 +2547,86 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C4">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D4">
-        <v>143.45</v>
+        <v>141.1228571428571</v>
       </c>
       <c r="E4">
-        <v>860.6999999999999</v>
+        <v>987.8599999999999</v>
       </c>
       <c r="F4">
-        <v>99.09999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="G4">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H4" t="s">
         <v>66</v>
       </c>
       <c r="I4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>61</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D5">
-        <v>147.6133333333333</v>
+        <v>132.3257142857143</v>
       </c>
       <c r="E5">
-        <v>885.6800000000001</v>
+        <v>926.28</v>
       </c>
       <c r="F5">
-        <v>98.09999999999999</v>
+        <v>89.60000000000001</v>
       </c>
       <c r="G5">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="H5" t="s">
         <v>67</v>
       </c>
       <c r="I5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C6">
-        <v>0.6666666666666666</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D6">
-        <v>132.2266666666667</v>
+        <v>142.4514285714286</v>
       </c>
       <c r="E6">
-        <v>793.36</v>
+        <v>997.1600000000001</v>
       </c>
       <c r="F6">
-        <v>95</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="G6">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="H6" t="s">
         <v>68</v>
       </c>
       <c r="I6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2549,25 +2637,25 @@
         <v>62</v>
       </c>
       <c r="C7">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D7">
-        <v>130.6033333333333</v>
+        <v>131.0085714285714</v>
       </c>
       <c r="E7">
-        <v>783.62</v>
+        <v>917.0599999999999</v>
       </c>
       <c r="F7">
-        <v>52.7</v>
+        <v>63</v>
       </c>
       <c r="G7">
-        <v>15.4</v>
+        <v>11.9</v>
       </c>
       <c r="H7" t="s">
         <v>69</v>
       </c>
       <c r="I7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2578,25 +2666,25 @@
         <v>63</v>
       </c>
       <c r="C8">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D8">
-        <v>134.0966666666667</v>
+        <v>134.4114285714286</v>
       </c>
       <c r="E8">
-        <v>804.58</v>
+        <v>940.8800000000001</v>
       </c>
       <c r="F8">
-        <v>42.9</v>
+        <v>44.8</v>
       </c>
       <c r="G8">
-        <v>22.4</v>
+        <v>24.5</v>
       </c>
       <c r="H8" t="s">
         <v>70</v>
       </c>
       <c r="I8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2607,19 +2695,19 @@
         <v>63</v>
       </c>
       <c r="C9">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D9">
-        <v>125.7433333333334</v>
+        <v>125.3542857142857</v>
       </c>
       <c r="E9">
-        <v>754.4600000000002</v>
+        <v>877.4800000000001</v>
       </c>
       <c r="F9">
-        <v>12.7</v>
+        <v>17.1</v>
       </c>
       <c r="G9">
-        <v>60.3</v>
+        <v>59.7</v>
       </c>
       <c r="H9" t="s">
         <v>71</v>
@@ -2660,7 +2748,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
@@ -2669,7 +2757,7 @@
         <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
         <v>81</v>
@@ -2680,16 +2768,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>82</v>
@@ -2700,7 +2788,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
         <v>48</v>
@@ -2709,10 +2797,10 @@
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2723,16 +2811,16 @@
         <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2743,16 +2831,16 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2760,19 +2848,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2780,19 +2868,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D8">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2803,16 +2891,16 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9">
         <v>-16</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -2822,111 +2910,123 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>-8</v>
+      </c>
+      <c r="C2">
+        <v>-6</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2">
+        <v>8</v>
+      </c>
+      <c r="H2">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>4</v>
+      </c>
+      <c r="H3">
+        <v>15</v>
+      </c>
+      <c r="I3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
+      <c r="B4">
         <v>9</v>
       </c>
-      <c r="C2">
-        <v>6</v>
-      </c>
-      <c r="D2">
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4">
         <v>14</v>
       </c>
-      <c r="E2">
+      <c r="E4">
         <v>15</v>
       </c>
-      <c r="F2">
+      <c r="F4">
         <v>20</v>
       </c>
-      <c r="G2">
+      <c r="G4">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>-8</v>
-      </c>
-      <c r="C3">
-        <v>-6</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-      <c r="H4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="H4">
+        <v>4</v>
+      </c>
+      <c r="I4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -2948,11 +3048,14 @@
       <c r="G5">
         <v>2</v>
       </c>
-      <c r="H5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -2974,63 +3077,72 @@
       <c r="G6">
         <v>0</v>
       </c>
-      <c r="H6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="H6">
+        <v>-3</v>
+      </c>
+      <c r="I6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>-6</v>
+      </c>
+      <c r="G7">
+        <v>-8</v>
+      </c>
+      <c r="H7">
+        <v>-8</v>
+      </c>
+      <c r="I7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
         <v>-3</v>
       </c>
-      <c r="C7">
+      <c r="C8">
         <v>-6</v>
       </c>
-      <c r="D7">
+      <c r="D8">
         <v>-8</v>
       </c>
-      <c r="E7">
+      <c r="E8">
         <v>-3</v>
       </c>
-      <c r="F7">
+      <c r="F8">
         <v>-4</v>
       </c>
-      <c r="G7">
+      <c r="G8">
         <v>-4</v>
       </c>
-      <c r="H7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>4</v>
-      </c>
-      <c r="D8">
-        <v>3</v>
-      </c>
-      <c r="E8">
-        <v>4</v>
-      </c>
-      <c r="F8">
-        <v>-6</v>
-      </c>
-      <c r="G8">
-        <v>-8</v>
-      </c>
-      <c r="H8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="H8">
+        <v>-12</v>
+      </c>
+      <c r="I8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -3052,8 +3164,11 @@
       <c r="G9">
         <v>-16</v>
       </c>
-      <c r="H9" t="s">
-        <v>85</v>
+      <c r="H9">
+        <v>-16</v>
+      </c>
+      <c r="I9" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Ross' Fantasy League 2026.xlsx
+++ b/data/leagues/Ross' Fantasy League 2026.xlsx
@@ -217,22 +217,22 @@
     <t>2-5</t>
   </si>
   <si>
-    <t>9.2-3.7-0.1</t>
+    <t>9.3-3.6-0.1</t>
   </si>
   <si>
     <t>9.0-3.9-0.1</t>
   </si>
   <si>
-    <t>7.2-5.8-0.1</t>
+    <t>7.1-5.8-0.1</t>
+  </si>
+  <si>
+    <t>6.2-6.8-0.1</t>
   </si>
   <si>
     <t>6.4-6.5-0.1</t>
   </si>
   <si>
-    <t>6.1-6.9-0.1</t>
-  </si>
-  <si>
-    <t>5.4-7.5-0.1</t>
+    <t>5.3-7.6-0.1</t>
   </si>
   <si>
     <t>4.5-8.4-0.1</t>
@@ -274,10 +274,10 @@
     <t>↑11</t>
   </si>
   <si>
+    <t>↑2</t>
+  </si>
+  <si>
     <t>↓11</t>
-  </si>
-  <si>
-    <t>↑2</t>
   </si>
   <si>
     <t>↓3</t>
@@ -1661,16 +1661,16 @@
         <v>60.3</v>
       </c>
       <c r="C2">
-        <v>30.6</v>
+        <v>29.5</v>
       </c>
       <c r="D2">
-        <v>6.6</v>
+        <v>7.7</v>
       </c>
       <c r="E2">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="F2">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G2">
         <v>0.2</v>
@@ -1690,22 +1690,22 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>35.3</v>
+        <v>34.5</v>
       </c>
       <c r="C3">
-        <v>49.4</v>
+        <v>50.7</v>
       </c>
       <c r="D3">
-        <v>11.2</v>
+        <v>10.1</v>
       </c>
       <c r="E3">
         <v>3.2</v>
       </c>
       <c r="F3">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="G3">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1722,95 +1722,95 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="C4">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="D4">
-        <v>40.2</v>
+        <v>38.3</v>
       </c>
       <c r="E4">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="F4">
-        <v>13.8</v>
+        <v>15.5</v>
       </c>
       <c r="G4">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="H4">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="I4">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="J4">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="C5">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="D5">
-        <v>14.6</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>24.5</v>
+        <v>26.4</v>
       </c>
       <c r="F5">
-        <v>27.5</v>
+        <v>22.1</v>
       </c>
       <c r="G5">
-        <v>19.4</v>
+        <v>16</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>5.6</v>
       </c>
       <c r="I5">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>89.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6">
         <v>1.2</v>
       </c>
       <c r="C6">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="D6">
-        <v>20.9</v>
+        <v>14.7</v>
       </c>
       <c r="E6">
-        <v>26.2</v>
+        <v>24.1</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>27.6</v>
       </c>
       <c r="G6">
-        <v>15.2</v>
+        <v>17.7</v>
       </c>
       <c r="H6">
-        <v>10.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I6">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J6">
-        <v>87.40000000000001</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1824,25 +1824,25 @@
         <v>0.5</v>
       </c>
       <c r="D7">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="E7">
         <v>12.7</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>17.9</v>
       </c>
       <c r="G7">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="H7">
-        <v>25.1</v>
+        <v>25.8</v>
       </c>
       <c r="I7">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
       <c r="J7">
-        <v>63</v>
+        <v>62.6</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1853,28 +1853,28 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="E8">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="F8">
-        <v>14</v>
+        <v>10.4</v>
       </c>
       <c r="G8">
-        <v>21.9</v>
+        <v>24.6</v>
       </c>
       <c r="H8">
-        <v>30.7</v>
+        <v>36</v>
       </c>
       <c r="I8">
-        <v>24.5</v>
+        <v>21</v>
       </c>
       <c r="J8">
-        <v>44.8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1888,25 +1888,25 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="E9">
         <v>1.5</v>
       </c>
       <c r="F9">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="G9">
-        <v>10.1</v>
+        <v>8</v>
       </c>
       <c r="H9">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="I9">
-        <v>59.7</v>
+        <v>62.1</v>
       </c>
       <c r="J9">
-        <v>17.1</v>
+        <v>15.1</v>
       </c>
     </row>
   </sheetData>
@@ -1947,16 +1947,16 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2">
-        <v>42.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="C2">
-        <v>99.90000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="D2">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="E2">
         <v>100</v>
@@ -1965,7 +1965,7 @@
         <v>100</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="H2">
         <v>100</v>
@@ -1976,31 +1976,31 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3">
-        <v>98.2</v>
+        <v>40.3</v>
       </c>
       <c r="C3">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D3">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="E3">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="F3">
         <v>100</v>
       </c>
       <c r="G3">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I3">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2011,83 +2011,83 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>94.3</v>
+        <v>93.30000000000001</v>
       </c>
       <c r="D4">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="E4">
-        <v>93.10000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="F4">
+        <v>98.8</v>
+      </c>
+      <c r="G4">
         <v>98.59999999999999</v>
       </c>
-      <c r="G4">
-        <v>99</v>
-      </c>
       <c r="H4">
-        <v>97.39999999999999</v>
+        <v>96</v>
       </c>
       <c r="I4">
-        <v>97.89999999999999</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C5">
-        <v>64.7</v>
+        <v>99.7</v>
       </c>
       <c r="D5">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="E5">
-        <v>59.9</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F5">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>92.90000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="H5">
-        <v>88.90000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="I5">
-        <v>90.40000000000001</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="C6">
-        <v>99.7</v>
+        <v>63.3</v>
       </c>
       <c r="D6">
-        <v>100</v>
+        <v>30.6</v>
       </c>
       <c r="E6">
-        <v>99.8</v>
+        <v>60.09999999999999</v>
       </c>
       <c r="F6">
-        <v>99.90000000000001</v>
+        <v>79.60000000000001</v>
       </c>
       <c r="G6">
-        <v>97.39999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H6">
-        <v>91.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I6">
-        <v>90</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2095,28 +2095,28 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>89.8</v>
+        <v>90.5</v>
       </c>
       <c r="C7">
-        <v>11.6</v>
+        <v>14.8</v>
       </c>
       <c r="D7">
-        <v>93.2</v>
+        <v>93.30000000000001</v>
       </c>
       <c r="E7">
-        <v>71</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F7">
-        <v>50.5</v>
+        <v>52.7</v>
       </c>
       <c r="G7">
-        <v>47.2</v>
+        <v>48.1</v>
       </c>
       <c r="H7">
-        <v>57.2</v>
+        <v>60</v>
       </c>
       <c r="I7">
-        <v>62.6</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2124,28 +2124,28 @@
         <v>0</v>
       </c>
       <c r="B8">
-        <v>88.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="C8">
-        <v>95.3</v>
+        <v>96.3</v>
       </c>
       <c r="D8">
-        <v>49.9</v>
+        <v>52.2</v>
       </c>
       <c r="E8">
-        <v>15.2</v>
+        <v>18</v>
       </c>
       <c r="F8">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="G8">
-        <v>47</v>
+        <v>48.1</v>
       </c>
       <c r="H8">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="I8">
-        <v>43.4</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2153,28 +2153,28 @@
         <v>6</v>
       </c>
       <c r="B9">
-        <v>85.09999999999999</v>
+        <v>84.89999999999999</v>
       </c>
       <c r="C9">
-        <v>36.5</v>
+        <v>34.3</v>
       </c>
       <c r="D9">
         <v>24.1</v>
       </c>
       <c r="E9">
-        <v>61.1</v>
+        <v>58.7</v>
       </c>
       <c r="F9">
-        <v>55.1</v>
+        <v>52.90000000000001</v>
       </c>
       <c r="G9">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H9">
-        <v>16.1</v>
+        <v>15.7</v>
       </c>
       <c r="I9">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
     </row>
   </sheetData>
@@ -2559,10 +2559,10 @@
         <v>987.8599999999999</v>
       </c>
       <c r="F4">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="G4">
-        <v>0.1</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H4" t="s">
         <v>66</v>
@@ -2573,25 +2573,25 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5">
-        <v>0.5714285714285714</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D5">
-        <v>132.3257142857143</v>
+        <v>142.4514285714286</v>
       </c>
       <c r="E5">
-        <v>926.28</v>
+        <v>997.1600000000001</v>
       </c>
       <c r="F5">
-        <v>89.60000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="G5">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H5" t="s">
         <v>67</v>
@@ -2602,25 +2602,25 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C6">
-        <v>0.4285714285714285</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D6">
-        <v>142.4514285714286</v>
+        <v>132.3257142857143</v>
       </c>
       <c r="E6">
-        <v>997.1600000000001</v>
+        <v>926.28</v>
       </c>
       <c r="F6">
-        <v>87.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="G6">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="H6" t="s">
         <v>68</v>
@@ -2646,10 +2646,10 @@
         <v>917.0599999999999</v>
       </c>
       <c r="F7">
-        <v>63</v>
+        <v>62.6</v>
       </c>
       <c r="G7">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
       <c r="H7" t="s">
         <v>69</v>
@@ -2675,16 +2675,16 @@
         <v>940.8800000000001</v>
       </c>
       <c r="F8">
-        <v>44.8</v>
+        <v>43</v>
       </c>
       <c r="G8">
-        <v>24.5</v>
+        <v>21</v>
       </c>
       <c r="H8" t="s">
         <v>70</v>
       </c>
       <c r="I8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2704,10 +2704,10 @@
         <v>877.4800000000001</v>
       </c>
       <c r="F9">
-        <v>17.1</v>
+        <v>15.1</v>
       </c>
       <c r="G9">
-        <v>59.7</v>
+        <v>62.1</v>
       </c>
       <c r="H9" t="s">
         <v>71</v>
@@ -2788,16 +2788,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D4">
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>83</v>
@@ -2808,16 +2808,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>84</v>
@@ -2999,25 +2999,25 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4">
         <v>2</v>
       </c>
-      <c r="B4">
-        <v>9</v>
-      </c>
       <c r="C4">
         <v>6</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>-3</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>-2</v>
       </c>
       <c r="G4">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H4">
         <v>4</v>
@@ -3028,25 +3028,25 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>6</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E5">
-        <v>-3</v>
+        <v>15</v>
       </c>
       <c r="F5">
-        <v>-2</v>
+        <v>20</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H5">
         <v>4</v>
